--- a/agrra_monitoring/data_raw/ATG_NPA_2025/Calculated/BenthicCoralRecruits.xlsx
+++ b/agrra_monitoring/data_raw/ATG_NPA_2025/Calculated/BenthicCoralRecruits.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\AGRRA\Sent Product Files\products\Calculated\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\AGRRA Group Work\Data Product Fix\Ruleo\NDNP2025\Calculated\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38AEF15C-D7A0-4DDE-8E0E-15A623A58E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{545DA146-5D0D-40D1-96E7-A6F845C30587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-45" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="TermsOfUse" sheetId="17" r:id="rId1"/>
+    <sheet name="TermsOfUse" sheetId="18" r:id="rId1"/>
     <sheet name="Metadata" sheetId="1" r:id="rId2"/>
     <sheet name="Overall" sheetId="2" r:id="rId3"/>
     <sheet name="tACRO" sheetId="3" r:id="rId4"/>
@@ -31,7 +31,7 @@
     <sheet name="tSIDE" sheetId="15" r:id="rId16"/>
     <sheet name="UNKN" sheetId="16" r:id="rId17"/>
   </sheets>
-  <calcPr calcId="999999"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -1693,12 +1693,40 @@
     <t>SIDEtotal</t>
   </si>
   <si>
-    <t>Created: 2025 Aug 8</t>
-  </si>
-  <si>
-    <t>Version 1.0</t>
-  </si>
-  <si>
+    <t>Created: 2026 May 29</t>
+  </si>
+  <si>
+    <t>AGRRA Terms of Data Service</t>
+  </si>
+  <si>
+    <t>The Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program champions coral reef conservation and empowers those who protect these diverse ecosystems. We are an international collaboration of scientists, managers, and supporters aimed at improving the regional condition of reefs in the Western Atlantic and Gulf of Mexico. For 25 years, AGRRA has used an innovative regional approach to examine the condition of reef-building corals, algae, and fishes, and support the conservation of coral reef ecosystems. We curate and distribute data, research and educational materials that support this mission. For more information, visit www.agrra.org or email info@agrra.org.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">AGRRA’s goal is to provide data contributors access to the AGRRA data platform, which provides: 
+a)	a standardized way to enter coral reef monitoring data with built in quality controls,
+b)	an efficient way to process data and visualize data through interactive graphics,
+c)	synthesized data products provided as RAW data and Calculated Products, and 
+d)	a centralized and secure place to manage and store data.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1. Ownership &amp; Intellectual Property</t>
+    </r>
     <r>
       <rPr>
         <b/>
@@ -1708,23 +1736,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Date produced: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">Data in this country batch were produced in collaboration with the batch owner: Ruleo Camacho. These data products are in draft form and are under review. Prior to data use, you need to accept the Terms and Conditions in the AGRRA Data License below. In addition, permission to distribute data must follow any data agreements required by the batch owner and/or individual surveyors who submitted data prior to use. </t>
-    </r>
-  </si>
-  <si>
-    <t>The Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program champions coral reef conservation and empowers those who protect these diverse ecosystems. We are an international collaboration of scientists, managers, and supporters aimed at improving the regional condition of reefs in the Western Atlantic and Gulf of Mexico. For 25 years, AGRRA has used an innovative regional approach to examine the condition of reef-building corals, algae and fishes and support the conservation of coral reef ecosystems. We curate and distribute data, research and educational materials that support this mission. For more information, visit www.agrra.org or email info@agrra.org.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Conditions of Use of AGRRA Data Products
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
@@ -1733,7 +1745,330 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">In order to use the AGRRA dataset, you need to accept the Terms and Conditions in the AGRRA Data License below.
+      <t xml:space="preserve">•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Original Observations:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> The raw data collected during surveys remains the intellectual property of the original data collectors and their respective organizations.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Methodology &amp; Systems: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">All protocols (Benthic, Coral, Fish), platform systems, AGRRA content, and related tools remain the intellectual property of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ocean Research &amp; Education Foundation, Inc. (ORE)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AGRRA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">, and their licensors, as applicable.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Processed Metrics: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">The calculated metrics, custom-coded logic, and standardized protocols used to generate these spreadsheets are the proprietary property of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AGRRA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> and the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ocean Research &amp; Education Foundation (ORE)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">User Content: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Users retain ownership of data, images, and other content they submit, but grant AGRRA the rights needed to store, process, share, and display that content in accordance with these terms.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. Data Sharing &amp; Privacy Publication Protocol
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">AGRRA is committed to protecting the privacy of the Data Contributors with respect to their data batches and offers three privacy options for each data batch:
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Data Batch Privacy Options: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Data Batches may be designated as Private, Public Summary, or Public. Some batch metadata may remain publicly visible to support transparency and attribution.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Accounts &amp; Security:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Data Contributors are responsible for their accounts, passwords, and all activity under their accounts, and must promptly report any suspected unauthorized access.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+3. Permitted Uses</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+•	Non-Commercial Use:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Data Contributors and Third-party Users (with permission) are licensed to use these materials and datasets for research, education, conservation, and other non-commercial purposes.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Commercial Use:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Commercial use, sale, or redistribution of AGRRA materials, datasets, or API outputs requires prior written permission.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Lawful and Responsible Use:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> All users must comply with applicable laws and must not misuse, disrupt, alter, scrape, or interfere with the platform, its software, security, or other users.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+4. Citation &amp; Acknowledgment
 </t>
     </r>
     <r>
@@ -1745,7 +2080,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>AGRRA Data License and Data Use Agreements</t>
+      <t>A. Guidance for Original Data Contributors</t>
     </r>
     <r>
       <rPr>
@@ -1754,7 +2089,167 @@
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">
-By accessing and using any of the datasets distributed by AGRRA, you acknowledge that you have read, understood, and agree to comply with the terms and conditions contained within this agreement. A Data Use Agreement (DUA) must be entered into before there is any use or distribution of a data set to an outside entity. AGRRA may amend these terms and conditions at any time. Your continued use of this data constitutes acceptance of the terms and conditions stated at the time of your use. You should contact AGRRA to determine the current terms and conditions to which you are bound.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>How to cite your data:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> When publishing, presenting, or otherwise sharing analyses based on your own contributed dataset, please cite the dataset using the suggested AGRRA format: [Surveyor Names/Organization], [Country] ([Year]). [Dataset Name/Region]. In: Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform, [Protocol Version Number] [Data Product Name]. [URL/DOI]. Accessed [Date].
+                o   Examples
+                         ▪For a specific survey: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Smith, J. &amp; Reef Care Bahamas, Bahamas (2024). New Providence Benthic Surveys. In: Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform, v5.2 Coral &amp; Benthic Data. www.agrra.org. Accessed May 14, 2026.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+                         ▪For an aggregated country-level report: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Belize Fisheries Department &amp; Healthy Reefs Initiative, Belize (2025). 2025 National Monitoring Data. In: Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform. www.agrra.org. Accessed May 2026.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>How to acknowledge AGRRA:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> In all publications and presentations using your contributed data, please acknowledge AGRRA as the platform that curates, manages, and provides access to the dataset.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Suggested acknowledgment language:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> "We acknowledge (or thank) the Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform for curating and providing access to the dataset used in this work."
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Collaboration:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Contributors are encouraged to remain available for collaboration when their expertise may strengthen data interpretation or publication.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Notification of use:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Please share an electronic copy of any final reports, publications, or presentations with AGRRA curated data to data@agrra.org.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
@@ -1766,7 +2261,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Data Permissions and Proprietary Rights to Content</t>
+      <t>B. Guidance for Third-Party Data Users</t>
     </r>
     <r>
       <rPr>
@@ -1775,8 +2270,8 @@
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">
-All datasets are the property of AGRRA and/or its affiliates, unless otherwise noted. With permission and DUA, you may use these datasets for non-commercial purposes, including research, education, presentations, and non-commercial publications. You understand and agree that you may not copy, reproduce, distribute or create derivative works for other purposes, without prior, written authorization from the AGRRA Project Leader. When using or publishing any parts of these datasets, proper acknowledgement of AGRRA and original source(s), is required.
-</t>
+Third-party users (not original data collectors) who would like to use an AGRRA data batch should first contact and obtain permission from the original data contributor and/or AGRRA at data@agrra.org. Once permission is granted, third-party users who utilize AGRRA-hosted data for research, presentations, reports, or publications shall give appropriate credit to both the original data contributors and AGRRA. The guidance below explains how to cite the original dataset and how to acknowledge AGRRA as the data platform.
+•	</t>
     </r>
     <r>
       <rPr>
@@ -1787,7 +2282,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Limitation of Liability</t>
+      <t xml:space="preserve">How to cite original data contributors: </t>
     </r>
     <r>
       <rPr>
@@ -1795,9 +2290,8 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">
-AGRRA makes reasonable efforts to provide accurate data and information through its website, database, and other channels. Nevertheless, you understand and agree that AGRRA shall not be liable for any loss or damage resulting from any use of, or inability to use, this data, or resulting from any errors or omissions in the data content.
-</t>
+      <t xml:space="preserve">Cite the dataset using the names of the original surveyors, organizations, country, year, and dataset title, following the AGRRA dataset citation format. AGRRA can provide guidance on the appropriate citation for the specific dataset used.
+•	</t>
     </r>
     <r>
       <rPr>
@@ -1808,7 +2302,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Data Citation </t>
+      <t>How to acknowledge AGRRA:</t>
     </r>
     <r>
       <rPr>
@@ -1816,9 +2310,8 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">
-For any use of AGRRA data or datasets managed by AGRRA, or for general reference to the project in peer-reviewed literature, use the citation specified in the data use policy or for general citation use the following format below to cite data retrieved from the AGRRA website or AGRRA database manager. 
-</t>
+      <t xml:space="preserve"> In addition to citing the original dataset, acknowledge the Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform as the system that curates, manages, and provides access to the data.
+•	</t>
     </r>
     <r>
       <rPr>
@@ -1829,7 +2322,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Citation:</t>
+      <t xml:space="preserve">Suggested acknowledgment language: </t>
     </r>
     <r>
       <rPr>
@@ -1837,8 +2330,8 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve"> AGRRA. 2024. Atlantic and Gulf Rapid Reef Assessment (AGRRA): An online database of AGRRA coral reef survey data. Available: http://agrra.org. (Accessed: Date [e.g., March 10, 2024]).
-</t>
+      <t xml:space="preserve">"We thank the original data contributors [insert surveyor and/or organization names, where available] and acknowledge the Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform for curating and providing access to the dataset used in this work."
+•	</t>
     </r>
     <r>
       <rPr>
@@ -1849,7 +2342,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Acknowledgement:</t>
+      <t>Direct contact and collaboration:</t>
     </r>
     <r>
       <rPr>
@@ -1857,11 +2350,30 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve"> For general data, use: “We thank the following data providers: Atlantic Gulf Rapid Reef Assessment (AGRRA) contributors and data managers…”. Where noted, individual data contributors should be included in acknowledgments. 
+      <t xml:space="preserve"> Third-party users are encouraged to contact the original data collectors to discuss collaboration or co-authorship, clarify interpretation, and share findings, where appropriate.
 </t>
     </r>
-  </si>
-  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+5. Liability &amp; Compliance
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">•	</t>
+    </r>
     <r>
       <rPr>
         <b/>
@@ -1871,7 +2383,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Data Use Policy</t>
+      <t>Data Integrity:</t>
     </r>
     <r>
       <rPr>
@@ -1879,19 +2391,9 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">
-Data collected under the auspices of AGRRA are available to the public after primary publication, or at most two years after the completion of the study unless proprietary restrictions are warranted. Request for the use of AGRRA data is to be made in writing and is subject to acceptance of the following conditions:
-1. The user agrees to provide valid name and contact information prior to requesting or downloading online data. This information will be used to ensure data agreements are in place, to contact the user in case of changes to the data, and may also be used by data set authors and AGRRA project administrators to document data usage.
-2. The user agrees to cite the data set author (if stated) and AGRRA in all publications in which the data are used, as per the instructions in “Data Citation”. 
-3. The user agrees to provide one copy of any manuscript based on AGRRA data to the AGRRA or data set author (if specified) prior to submitting it for peer-reviewed publication.
-4. The user also agrees to send one electronic copy or reports or publication (pdf format) to: data@agrra.org and gis@agrra.org. 
-5. Users are prohibited from selling or redistributing any data provided by AGRRA without explicit prior permission.
-6. If specified, users are to contact original investigators or data contributors responsible for data prior to data use, and where appropriate, are encouraged to consider collaboration and/or co-authorship with original investigators.
-7. Extensive efforts are made to ensure that data products are accurate and up to date, but the authors and AGRRA will not take responsibility for any errors that may exist in data provided. The user assumes all responsibility for errors in analysis or judgment resulting from use of the data.
-8. Any violation of the terms of this agreement will result in immediate forfeiture of the data and loss of access privileges to other AGRRA data sets.  </t>
+      <t xml:space="preserve"> AGRRA works diligently to maintain data accuracy; however, Data Contributors and Third-Party users are responsible for their own analyses, interpretations, and resulting conclusions.
+•	</t>
     </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -1901,7 +2403,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Format of Data:</t>
+      <t>No Warranty:</t>
     </r>
     <r>
       <rPr>
@@ -1909,8 +2411,71 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve"> Original data is submitted into the data portal by surveyors trained in the AGRRA method to maintain data accuracy and consistency. AGRRA provides data products as raw products and as calculated products. Note these are draft data products from the beta version of the new AGRRA data portal (2024) and are currently in review. AGRRA reserves the right to update data products as needed.  Contact AGRRA if you have questions.</t>
+      <t xml:space="preserve"> The platform, data, and related content are provided “as is” and “as available,” without guarantees of accuracy, availability, security, or fitness for a particular purpose.
+•	</t>
     </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Limitation of Liability:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> AGRRA and its operators are not liable for indirect, incidental, consequential, or data-loss-related damages arising from the use of the platform.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Access Review: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">If these terms are not followed, AGRRA reserves the right to review, suspend, modify, or terminate access privileges or service availability as appropriate.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Changes &amp; Governing Law:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> AGRRA may update these terms from time to time; continued use represents acceptance. </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">           </t>
   </si>
   <si>
     <r>
@@ -1934,23 +2499,30 @@
     </r>
   </si>
   <si>
+    <t>Version 1.0</t>
+  </si>
+  <si>
+    <t>Data provided in these country batches were produced in collaboration with the batch owner: Ruleo Camacho. Prior to data use, you need to accept the Terms and Conditions in the AGRRA Terms of Data Service below. In addition, permission to distribute data must follow any data agreements required by the batch owner and/or individual surveyors who submitted data prior to use.</t>
+  </si>
+  <si>
     <r>
       <rPr>
+        <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
-      <t>©</t>
+      <t>Format of Data:</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Ocean Research and Education Foundation</t>
+      <t xml:space="preserve"> Original data is submitted into the data portal by surveyors trained in the AGRRA method to maintain data accuracy and consistency. AGRRA provides data products as raw products and as calculated products. AGRRA reserves the right to update data products as needed.  Contact AGRRA if you have questions.</t>
     </r>
   </si>
 </sst>
@@ -1961,11 +2533,18 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0#"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1989,16 +2568,35 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -2021,7 +2619,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -2039,6 +2637,66 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -2048,7 +2706,22 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -2171,16 +2844,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -2199,13 +2873,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2214,117 +2891,105 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{DDD2BCF7-D557-4251-8A7D-AE78274F9708}"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{B27F8426-3119-4488-81B7-781C5F22CC95}"/>
+    <cellStyle name="Normal 2 2" xfId="2" xr:uid="{E00711AD-EAB4-4426-9E34-A18580051E0D}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
@@ -2337,61 +3002,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>257176</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>180976</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>322132</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>123826</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B88B7AC-966F-4A6A-9C7D-8FE8277CED6A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6276976" y="180976"/>
-          <a:ext cx="2655756" cy="2038350"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2680,1051 +3290,1601 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0DA1C7D-2F69-4C2B-ABF9-22DD4A027BED}">
-  <dimension ref="A1:W78"/>
-  <sheetFormatPr defaultColWidth="9.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{515497F4-E678-417E-BE38-87CCA415261C}">
+  <dimension ref="A1:X70"/>
+  <sheetFormatPr defaultColWidth="9.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" style="16" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" style="16" customWidth="1"/>
-    <col min="3" max="16384" width="9.7109375" style="16"/>
+    <col min="2" max="2" width="11.26953125" style="16" customWidth="1"/>
+    <col min="3" max="16384" width="9.7265625" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A1" s="15" t="s">
         <v>543</v>
       </c>
       <c r="B1" s="15"/>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
+        <v>549</v>
+      </c>
+      <c r="B2" s="15"/>
+    </row>
+    <row r="4" spans="1:23" ht="19.5" x14ac:dyDescent="0.45">
+      <c r="A4" s="17" t="s">
         <v>544</v>
       </c>
-      <c r="B2" s="15"/>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="18"/>
+      <c r="P4" s="18"/>
+      <c r="Q4" s="18"/>
+      <c r="R4" s="18"/>
+      <c r="S4" s="18"/>
+      <c r="T4" s="18"/>
+      <c r="U4" s="18"/>
+      <c r="V4" s="18"/>
+      <c r="W4" s="18"/>
+    </row>
+    <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A6" s="19" t="s">
+        <v>550</v>
+      </c>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20"/>
+      <c r="R6" s="20"/>
+      <c r="S6" s="20"/>
+      <c r="T6" s="20"/>
+      <c r="U6" s="20"/>
+      <c r="V6" s="20"/>
+      <c r="W6" s="21"/>
+    </row>
+    <row r="7" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="22"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="23"/>
+      <c r="S7" s="23"/>
+      <c r="T7" s="23"/>
+      <c r="U7" s="23"/>
+      <c r="V7" s="23"/>
+      <c r="W7" s="24"/>
+    </row>
+    <row r="8" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:23" ht="53.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="25" t="s">
         <v>545</v>
       </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="17"/>
-      <c r="R13" s="17"/>
-      <c r="S13" s="17"/>
-      <c r="T13" s="17"/>
-      <c r="U13" s="17"/>
-      <c r="V13" s="17"/>
-      <c r="W13" s="17"/>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="17"/>
-      <c r="R14" s="17"/>
-      <c r="S14" s="17"/>
-      <c r="T14" s="17"/>
-      <c r="U14" s="17"/>
-      <c r="V14" s="17"/>
-      <c r="W14" s="17"/>
-    </row>
-    <row r="15" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:23" ht="58.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="18" t="s">
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="26"/>
+      <c r="O9" s="26"/>
+      <c r="P9" s="26"/>
+      <c r="Q9" s="26"/>
+      <c r="R9" s="26"/>
+      <c r="S9" s="26"/>
+      <c r="T9" s="26"/>
+      <c r="U9" s="26"/>
+      <c r="V9" s="26"/>
+      <c r="W9" s="27"/>
+    </row>
+    <row r="10" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="28" t="s">
         <v>546</v>
       </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="19"/>
-      <c r="Q16" s="19"/>
-      <c r="R16" s="19"/>
-      <c r="S16" s="19"/>
-      <c r="T16" s="19"/>
-      <c r="U16" s="19"/>
-      <c r="V16" s="19"/>
-      <c r="W16" s="20"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="29"/>
+      <c r="O10" s="29"/>
+      <c r="P10" s="29"/>
+      <c r="Q10" s="29"/>
+      <c r="R10" s="29"/>
+      <c r="S10" s="29"/>
+      <c r="T10" s="29"/>
+      <c r="U10" s="29"/>
+      <c r="V10" s="29"/>
+      <c r="W10" s="30"/>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A11" s="31"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32"/>
+      <c r="L11" s="32"/>
+      <c r="M11" s="32"/>
+      <c r="N11" s="32"/>
+      <c r="O11" s="32"/>
+      <c r="P11" s="32"/>
+      <c r="Q11" s="32"/>
+      <c r="R11" s="32"/>
+      <c r="S11" s="32"/>
+      <c r="T11" s="32"/>
+      <c r="U11" s="32"/>
+      <c r="V11" s="32"/>
+      <c r="W11" s="33"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A12" s="31"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="32"/>
+      <c r="M12" s="32"/>
+      <c r="N12" s="32"/>
+      <c r="O12" s="32"/>
+      <c r="P12" s="32"/>
+      <c r="Q12" s="32"/>
+      <c r="R12" s="32"/>
+      <c r="S12" s="32"/>
+      <c r="T12" s="32"/>
+      <c r="U12" s="32"/>
+      <c r="V12" s="32"/>
+      <c r="W12" s="33"/>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A13" s="31"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="32"/>
+      <c r="P13" s="32"/>
+      <c r="Q13" s="32"/>
+      <c r="R13" s="32"/>
+      <c r="S13" s="32"/>
+      <c r="T13" s="32"/>
+      <c r="U13" s="32"/>
+      <c r="V13" s="32"/>
+      <c r="W13" s="33"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A14" s="31"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="32"/>
+      <c r="L14" s="32"/>
+      <c r="M14" s="32"/>
+      <c r="N14" s="32"/>
+      <c r="O14" s="32"/>
+      <c r="P14" s="32"/>
+      <c r="Q14" s="32"/>
+      <c r="R14" s="32"/>
+      <c r="S14" s="32"/>
+      <c r="T14" s="32"/>
+      <c r="U14" s="32"/>
+      <c r="V14" s="32"/>
+      <c r="W14" s="33"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A15" s="31"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
+      <c r="T15" s="32"/>
+      <c r="U15" s="32"/>
+      <c r="V15" s="32"/>
+      <c r="W15" s="33"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A16" s="31"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="32"/>
+      <c r="K16" s="32"/>
+      <c r="L16" s="32"/>
+      <c r="M16" s="32"/>
+      <c r="N16" s="32"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="32"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="32"/>
+      <c r="S16" s="32"/>
+      <c r="T16" s="32"/>
+      <c r="U16" s="32"/>
+      <c r="V16" s="32"/>
+      <c r="W16" s="33"/>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A17" s="31"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="32"/>
+      <c r="J17" s="32"/>
+      <c r="K17" s="32"/>
+      <c r="L17" s="32"/>
+      <c r="M17" s="32"/>
+      <c r="N17" s="32"/>
+      <c r="O17" s="32"/>
+      <c r="P17" s="32"/>
+      <c r="Q17" s="32"/>
+      <c r="R17" s="32"/>
+      <c r="S17" s="32"/>
+      <c r="T17" s="32"/>
+      <c r="U17" s="32"/>
+      <c r="V17" s="32"/>
+      <c r="W17" s="33"/>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A18" s="31"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="32"/>
+      <c r="K18" s="32"/>
+      <c r="L18" s="32"/>
+      <c r="M18" s="32"/>
+      <c r="N18" s="32"/>
+      <c r="O18" s="32"/>
+      <c r="P18" s="32"/>
+      <c r="Q18" s="32"/>
+      <c r="R18" s="32"/>
+      <c r="S18" s="32"/>
+      <c r="T18" s="32"/>
+      <c r="U18" s="32"/>
+      <c r="V18" s="32"/>
+      <c r="W18" s="33"/>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A19" s="31"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="32"/>
+      <c r="K19" s="32"/>
+      <c r="L19" s="32"/>
+      <c r="M19" s="32"/>
+      <c r="N19" s="32"/>
+      <c r="O19" s="32"/>
+      <c r="P19" s="32"/>
+      <c r="Q19" s="32"/>
+      <c r="R19" s="32"/>
+      <c r="S19" s="32"/>
+      <c r="T19" s="32"/>
+      <c r="U19" s="32"/>
+      <c r="V19" s="32"/>
+      <c r="W19" s="33"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A20" s="31"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="32"/>
+      <c r="M20" s="32"/>
+      <c r="N20" s="32"/>
+      <c r="O20" s="32"/>
+      <c r="P20" s="32"/>
+      <c r="Q20" s="32"/>
+      <c r="R20" s="32"/>
+      <c r="S20" s="32"/>
+      <c r="T20" s="32"/>
+      <c r="U20" s="32"/>
+      <c r="V20" s="32"/>
+      <c r="W20" s="33"/>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A21" s="31"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="32"/>
+      <c r="N21" s="32"/>
+      <c r="O21" s="32"/>
+      <c r="P21" s="32"/>
+      <c r="Q21" s="32"/>
+      <c r="R21" s="32"/>
+      <c r="S21" s="32"/>
+      <c r="T21" s="32"/>
+      <c r="U21" s="32"/>
+      <c r="V21" s="32"/>
+      <c r="W21" s="33"/>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A22" s="31"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="32"/>
+      <c r="K22" s="32"/>
+      <c r="L22" s="32"/>
+      <c r="M22" s="32"/>
+      <c r="N22" s="32"/>
+      <c r="O22" s="32"/>
+      <c r="P22" s="32"/>
+      <c r="Q22" s="32"/>
+      <c r="R22" s="32"/>
+      <c r="S22" s="32"/>
+      <c r="T22" s="32"/>
+      <c r="U22" s="32"/>
+      <c r="V22" s="32"/>
+      <c r="W22" s="33"/>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A23" s="31"/>
+      <c r="B23" s="32"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
+      <c r="L23" s="32"/>
+      <c r="M23" s="32"/>
+      <c r="N23" s="32"/>
+      <c r="O23" s="32"/>
+      <c r="P23" s="32"/>
+      <c r="Q23" s="32"/>
+      <c r="R23" s="32"/>
+      <c r="S23" s="32"/>
+      <c r="T23" s="32"/>
+      <c r="U23" s="32"/>
+      <c r="V23" s="32"/>
+      <c r="W23" s="33"/>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A24" s="31"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="32"/>
+      <c r="L24" s="32"/>
+      <c r="M24" s="32"/>
+      <c r="N24" s="32"/>
+      <c r="O24" s="32"/>
+      <c r="P24" s="32"/>
+      <c r="Q24" s="32"/>
+      <c r="R24" s="32"/>
+      <c r="S24" s="32"/>
+      <c r="T24" s="32"/>
+      <c r="U24" s="32"/>
+      <c r="V24" s="32"/>
+      <c r="W24" s="33"/>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A25" s="31"/>
+      <c r="B25" s="32"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="32"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="32"/>
+      <c r="M25" s="32"/>
+      <c r="N25" s="32"/>
+      <c r="O25" s="32"/>
+      <c r="P25" s="32"/>
+      <c r="Q25" s="32"/>
+      <c r="R25" s="32"/>
+      <c r="S25" s="32"/>
+      <c r="T25" s="32"/>
+      <c r="U25" s="32"/>
+      <c r="V25" s="32"/>
+      <c r="W25" s="33"/>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A26" s="31"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
+      <c r="L26" s="32"/>
+      <c r="M26" s="32"/>
+      <c r="N26" s="32"/>
+      <c r="O26" s="32"/>
+      <c r="P26" s="32"/>
+      <c r="Q26" s="32"/>
+      <c r="R26" s="32"/>
+      <c r="S26" s="32"/>
+      <c r="T26" s="32"/>
+      <c r="U26" s="32"/>
+      <c r="V26" s="32"/>
+      <c r="W26" s="33"/>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A27" s="31"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="32"/>
+      <c r="L27" s="32"/>
+      <c r="M27" s="32"/>
+      <c r="N27" s="32"/>
+      <c r="O27" s="32"/>
+      <c r="P27" s="32"/>
+      <c r="Q27" s="32"/>
+      <c r="R27" s="32"/>
+      <c r="S27" s="32"/>
+      <c r="T27" s="32"/>
+      <c r="U27" s="32"/>
+      <c r="V27" s="32"/>
+      <c r="W27" s="33"/>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A28" s="31"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
+      <c r="T28" s="32"/>
+      <c r="U28" s="32"/>
+      <c r="V28" s="32"/>
+      <c r="W28" s="33"/>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A29" s="31"/>
+      <c r="B29" s="32"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="32"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="32"/>
+      <c r="L29" s="32"/>
+      <c r="M29" s="32"/>
+      <c r="N29" s="32"/>
+      <c r="O29" s="32"/>
+      <c r="P29" s="32"/>
+      <c r="Q29" s="32"/>
+      <c r="R29" s="32"/>
+      <c r="S29" s="32"/>
+      <c r="T29" s="32"/>
+      <c r="U29" s="32"/>
+      <c r="V29" s="32"/>
+      <c r="W29" s="33"/>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A30" s="31"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="32"/>
+      <c r="J30" s="32"/>
+      <c r="K30" s="32"/>
+      <c r="L30" s="32"/>
+      <c r="M30" s="32"/>
+      <c r="N30" s="32"/>
+      <c r="O30" s="32"/>
+      <c r="P30" s="32"/>
+      <c r="Q30" s="32"/>
+      <c r="R30" s="32"/>
+      <c r="S30" s="32"/>
+      <c r="T30" s="32"/>
+      <c r="U30" s="32"/>
+      <c r="V30" s="32"/>
+      <c r="W30" s="33"/>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A31" s="31"/>
+      <c r="B31" s="32"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="32"/>
+      <c r="J31" s="32"/>
+      <c r="K31" s="32"/>
+      <c r="L31" s="32"/>
+      <c r="M31" s="32"/>
+      <c r="N31" s="32"/>
+      <c r="O31" s="32"/>
+      <c r="P31" s="32"/>
+      <c r="Q31" s="32"/>
+      <c r="R31" s="32"/>
+      <c r="S31" s="32"/>
+      <c r="T31" s="32"/>
+      <c r="U31" s="32"/>
+      <c r="V31" s="32"/>
+      <c r="W31" s="33"/>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A32" s="31"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="32"/>
+      <c r="J32" s="32"/>
+      <c r="K32" s="32"/>
+      <c r="L32" s="32"/>
+      <c r="M32" s="32"/>
+      <c r="N32" s="32"/>
+      <c r="O32" s="32"/>
+      <c r="P32" s="32"/>
+      <c r="Q32" s="32"/>
+      <c r="R32" s="32"/>
+      <c r="S32" s="32"/>
+      <c r="T32" s="32"/>
+      <c r="U32" s="32"/>
+      <c r="V32" s="32"/>
+      <c r="W32" s="33"/>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A33" s="31"/>
+      <c r="B33" s="32"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
+      <c r="J33" s="32"/>
+      <c r="K33" s="32"/>
+      <c r="L33" s="32"/>
+      <c r="M33" s="32"/>
+      <c r="N33" s="32"/>
+      <c r="O33" s="32"/>
+      <c r="P33" s="32"/>
+      <c r="Q33" s="32"/>
+      <c r="R33" s="32"/>
+      <c r="S33" s="32"/>
+      <c r="T33" s="32"/>
+      <c r="U33" s="32"/>
+      <c r="V33" s="32"/>
+      <c r="W33" s="33"/>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A34" s="31"/>
+      <c r="B34" s="32"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="32"/>
+      <c r="J34" s="32"/>
+      <c r="K34" s="32"/>
+      <c r="L34" s="32"/>
+      <c r="M34" s="32"/>
+      <c r="N34" s="32"/>
+      <c r="O34" s="32"/>
+      <c r="P34" s="32"/>
+      <c r="Q34" s="32"/>
+      <c r="R34" s="32"/>
+      <c r="S34" s="32"/>
+      <c r="T34" s="32"/>
+      <c r="U34" s="32"/>
+      <c r="V34" s="32"/>
+      <c r="W34" s="33"/>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A35" s="31"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="32"/>
+      <c r="J35" s="32"/>
+      <c r="K35" s="32"/>
+      <c r="L35" s="32"/>
+      <c r="M35" s="32"/>
+      <c r="N35" s="32"/>
+      <c r="O35" s="32"/>
+      <c r="P35" s="32"/>
+      <c r="Q35" s="32"/>
+      <c r="R35" s="32"/>
+      <c r="S35" s="32"/>
+      <c r="T35" s="32"/>
+      <c r="U35" s="32"/>
+      <c r="V35" s="32"/>
+      <c r="W35" s="33"/>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A36" s="31"/>
+      <c r="B36" s="32"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
+      <c r="J36" s="32"/>
+      <c r="K36" s="32"/>
+      <c r="L36" s="32"/>
+      <c r="M36" s="32"/>
+      <c r="N36" s="32"/>
+      <c r="O36" s="32"/>
+      <c r="P36" s="32"/>
+      <c r="Q36" s="32"/>
+      <c r="R36" s="32"/>
+      <c r="S36" s="32"/>
+      <c r="T36" s="32"/>
+      <c r="U36" s="32"/>
+      <c r="V36" s="32"/>
+      <c r="W36" s="33"/>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A37" s="31"/>
+      <c r="B37" s="32"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="32"/>
+      <c r="J37" s="32"/>
+      <c r="K37" s="32"/>
+      <c r="L37" s="32"/>
+      <c r="M37" s="32"/>
+      <c r="N37" s="32"/>
+      <c r="O37" s="32"/>
+      <c r="P37" s="32"/>
+      <c r="Q37" s="32"/>
+      <c r="R37" s="32"/>
+      <c r="S37" s="32"/>
+      <c r="T37" s="32"/>
+      <c r="U37" s="32"/>
+      <c r="V37" s="32"/>
+      <c r="W37" s="33"/>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A38" s="31"/>
+      <c r="B38" s="32"/>
+      <c r="C38" s="32"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="32"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="32"/>
+      <c r="I38" s="32"/>
+      <c r="J38" s="32"/>
+      <c r="K38" s="32"/>
+      <c r="L38" s="32"/>
+      <c r="M38" s="32"/>
+      <c r="N38" s="32"/>
+      <c r="O38" s="32"/>
+      <c r="P38" s="32"/>
+      <c r="Q38" s="32"/>
+      <c r="R38" s="32"/>
+      <c r="S38" s="32"/>
+      <c r="T38" s="32"/>
+      <c r="U38" s="32"/>
+      <c r="V38" s="32"/>
+      <c r="W38" s="33"/>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A39" s="31"/>
+      <c r="B39" s="32"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="32"/>
+      <c r="J39" s="32"/>
+      <c r="K39" s="32"/>
+      <c r="L39" s="32"/>
+      <c r="M39" s="32"/>
+      <c r="N39" s="32"/>
+      <c r="O39" s="32"/>
+      <c r="P39" s="32"/>
+      <c r="Q39" s="32"/>
+      <c r="R39" s="32"/>
+      <c r="S39" s="32"/>
+      <c r="T39" s="32"/>
+      <c r="U39" s="32"/>
+      <c r="V39" s="32"/>
+      <c r="W39" s="33"/>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A40" s="31"/>
+      <c r="B40" s="32"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="32"/>
+      <c r="J40" s="32"/>
+      <c r="K40" s="32"/>
+      <c r="L40" s="32"/>
+      <c r="M40" s="32"/>
+      <c r="N40" s="32"/>
+      <c r="O40" s="32"/>
+      <c r="P40" s="32"/>
+      <c r="Q40" s="32"/>
+      <c r="R40" s="32"/>
+      <c r="S40" s="32"/>
+      <c r="T40" s="32"/>
+      <c r="U40" s="32"/>
+      <c r="V40" s="32"/>
+      <c r="W40" s="33"/>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A41" s="31"/>
+      <c r="B41" s="32"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="32"/>
+      <c r="F41" s="32"/>
+      <c r="G41" s="32"/>
+      <c r="H41" s="32"/>
+      <c r="I41" s="32"/>
+      <c r="J41" s="32"/>
+      <c r="K41" s="32"/>
+      <c r="L41" s="32"/>
+      <c r="M41" s="32"/>
+      <c r="N41" s="32"/>
+      <c r="O41" s="32"/>
+      <c r="P41" s="32"/>
+      <c r="Q41" s="32"/>
+      <c r="R41" s="32"/>
+      <c r="S41" s="32"/>
+      <c r="T41" s="32"/>
+      <c r="U41" s="32"/>
+      <c r="V41" s="32"/>
+      <c r="W41" s="33"/>
+      <c r="X41" s="16" t="s">
         <v>547</v>
       </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="24" t="s">
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A42" s="31"/>
+      <c r="B42" s="32"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="32"/>
+      <c r="J42" s="32"/>
+      <c r="K42" s="32"/>
+      <c r="L42" s="32"/>
+      <c r="M42" s="32"/>
+      <c r="N42" s="32"/>
+      <c r="O42" s="32"/>
+      <c r="P42" s="32"/>
+      <c r="Q42" s="32"/>
+      <c r="R42" s="32"/>
+      <c r="S42" s="32"/>
+      <c r="T42" s="32"/>
+      <c r="U42" s="32"/>
+      <c r="V42" s="32"/>
+      <c r="W42" s="33"/>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A43" s="31"/>
+      <c r="B43" s="32"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="32"/>
+      <c r="J43" s="32"/>
+      <c r="K43" s="32"/>
+      <c r="L43" s="32"/>
+      <c r="M43" s="32"/>
+      <c r="N43" s="32"/>
+      <c r="O43" s="32"/>
+      <c r="P43" s="32"/>
+      <c r="Q43" s="32"/>
+      <c r="R43" s="32"/>
+      <c r="S43" s="32"/>
+      <c r="T43" s="32"/>
+      <c r="U43" s="32"/>
+      <c r="V43" s="32"/>
+      <c r="W43" s="33"/>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A44" s="31"/>
+      <c r="B44" s="32"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="32"/>
+      <c r="E44" s="32"/>
+      <c r="F44" s="32"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="32"/>
+      <c r="I44" s="32"/>
+      <c r="J44" s="32"/>
+      <c r="K44" s="32"/>
+      <c r="L44" s="32"/>
+      <c r="M44" s="32"/>
+      <c r="N44" s="32"/>
+      <c r="O44" s="32"/>
+      <c r="P44" s="32"/>
+      <c r="Q44" s="32"/>
+      <c r="R44" s="32"/>
+      <c r="S44" s="32"/>
+      <c r="T44" s="32"/>
+      <c r="U44" s="32"/>
+      <c r="V44" s="32"/>
+      <c r="W44" s="33"/>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A45" s="31"/>
+      <c r="B45" s="32"/>
+      <c r="C45" s="32"/>
+      <c r="D45" s="32"/>
+      <c r="E45" s="32"/>
+      <c r="F45" s="32"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="32"/>
+      <c r="I45" s="32"/>
+      <c r="J45" s="32"/>
+      <c r="K45" s="32"/>
+      <c r="L45" s="32"/>
+      <c r="M45" s="32"/>
+      <c r="N45" s="32"/>
+      <c r="O45" s="32"/>
+      <c r="P45" s="32"/>
+      <c r="Q45" s="32"/>
+      <c r="R45" s="32"/>
+      <c r="S45" s="32"/>
+      <c r="T45" s="32"/>
+      <c r="U45" s="32"/>
+      <c r="V45" s="32"/>
+      <c r="W45" s="33"/>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A46" s="31"/>
+      <c r="B46" s="32"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="32"/>
+      <c r="J46" s="32"/>
+      <c r="K46" s="32"/>
+      <c r="L46" s="32"/>
+      <c r="M46" s="32"/>
+      <c r="N46" s="32"/>
+      <c r="O46" s="32"/>
+      <c r="P46" s="32"/>
+      <c r="Q46" s="32"/>
+      <c r="R46" s="32"/>
+      <c r="S46" s="32"/>
+      <c r="T46" s="32"/>
+      <c r="U46" s="32"/>
+      <c r="V46" s="32"/>
+      <c r="W46" s="33"/>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A47" s="31"/>
+      <c r="B47" s="32"/>
+      <c r="C47" s="32"/>
+      <c r="D47" s="32"/>
+      <c r="E47" s="32"/>
+      <c r="F47" s="32"/>
+      <c r="G47" s="32"/>
+      <c r="H47" s="32"/>
+      <c r="I47" s="32"/>
+      <c r="J47" s="32"/>
+      <c r="K47" s="32"/>
+      <c r="L47" s="32"/>
+      <c r="M47" s="32"/>
+      <c r="N47" s="32"/>
+      <c r="O47" s="32"/>
+      <c r="P47" s="32"/>
+      <c r="Q47" s="32"/>
+      <c r="R47" s="32"/>
+      <c r="S47" s="32"/>
+      <c r="T47" s="32"/>
+      <c r="U47" s="32"/>
+      <c r="V47" s="32"/>
+      <c r="W47" s="33"/>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A48" s="31"/>
+      <c r="B48" s="32"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="32"/>
+      <c r="E48" s="32"/>
+      <c r="F48" s="32"/>
+      <c r="G48" s="32"/>
+      <c r="H48" s="32"/>
+      <c r="I48" s="32"/>
+      <c r="J48" s="32"/>
+      <c r="K48" s="32"/>
+      <c r="L48" s="32"/>
+      <c r="M48" s="32"/>
+      <c r="N48" s="32"/>
+      <c r="O48" s="32"/>
+      <c r="P48" s="32"/>
+      <c r="Q48" s="32"/>
+      <c r="R48" s="32"/>
+      <c r="S48" s="32"/>
+      <c r="T48" s="32"/>
+      <c r="U48" s="32"/>
+      <c r="V48" s="32"/>
+      <c r="W48" s="33"/>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A49" s="31"/>
+      <c r="B49" s="32"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="32"/>
+      <c r="I49" s="32"/>
+      <c r="J49" s="32"/>
+      <c r="K49" s="32"/>
+      <c r="L49" s="32"/>
+      <c r="M49" s="32"/>
+      <c r="N49" s="32"/>
+      <c r="O49" s="32"/>
+      <c r="P49" s="32"/>
+      <c r="Q49" s="32"/>
+      <c r="R49" s="32"/>
+      <c r="S49" s="32"/>
+      <c r="T49" s="32"/>
+      <c r="U49" s="32"/>
+      <c r="V49" s="32"/>
+      <c r="W49" s="33"/>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A50" s="31"/>
+      <c r="B50" s="32"/>
+      <c r="C50" s="32"/>
+      <c r="D50" s="32"/>
+      <c r="E50" s="32"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32"/>
+      <c r="I50" s="32"/>
+      <c r="J50" s="32"/>
+      <c r="K50" s="32"/>
+      <c r="L50" s="32"/>
+      <c r="M50" s="32"/>
+      <c r="N50" s="32"/>
+      <c r="O50" s="32"/>
+      <c r="P50" s="32"/>
+      <c r="Q50" s="32"/>
+      <c r="R50" s="32"/>
+      <c r="S50" s="32"/>
+      <c r="T50" s="32"/>
+      <c r="U50" s="32"/>
+      <c r="V50" s="32"/>
+      <c r="W50" s="33"/>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A51" s="31"/>
+      <c r="B51" s="32"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="32"/>
+      <c r="E51" s="32"/>
+      <c r="F51" s="32"/>
+      <c r="G51" s="32"/>
+      <c r="H51" s="32"/>
+      <c r="I51" s="32"/>
+      <c r="J51" s="32"/>
+      <c r="K51" s="32"/>
+      <c r="L51" s="32"/>
+      <c r="M51" s="32"/>
+      <c r="N51" s="32"/>
+      <c r="O51" s="32"/>
+      <c r="P51" s="32"/>
+      <c r="Q51" s="32"/>
+      <c r="R51" s="32"/>
+      <c r="S51" s="32"/>
+      <c r="T51" s="32"/>
+      <c r="U51" s="32"/>
+      <c r="V51" s="32"/>
+      <c r="W51" s="33"/>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A52" s="31"/>
+      <c r="B52" s="32"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="32"/>
+      <c r="E52" s="32"/>
+      <c r="F52" s="32"/>
+      <c r="G52" s="32"/>
+      <c r="H52" s="32"/>
+      <c r="I52" s="32"/>
+      <c r="J52" s="32"/>
+      <c r="K52" s="32"/>
+      <c r="L52" s="32"/>
+      <c r="M52" s="32"/>
+      <c r="N52" s="32"/>
+      <c r="O52" s="32"/>
+      <c r="P52" s="32"/>
+      <c r="Q52" s="32"/>
+      <c r="R52" s="32"/>
+      <c r="S52" s="32"/>
+      <c r="T52" s="32"/>
+      <c r="U52" s="32"/>
+      <c r="V52" s="32"/>
+      <c r="W52" s="33"/>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A53" s="31"/>
+      <c r="B53" s="32"/>
+      <c r="C53" s="32"/>
+      <c r="D53" s="32"/>
+      <c r="E53" s="32"/>
+      <c r="F53" s="32"/>
+      <c r="G53" s="32"/>
+      <c r="H53" s="32"/>
+      <c r="I53" s="32"/>
+      <c r="J53" s="32"/>
+      <c r="K53" s="32"/>
+      <c r="L53" s="32"/>
+      <c r="M53" s="32"/>
+      <c r="N53" s="32"/>
+      <c r="O53" s="32"/>
+      <c r="P53" s="32"/>
+      <c r="Q53" s="32"/>
+      <c r="R53" s="32"/>
+      <c r="S53" s="32"/>
+      <c r="T53" s="32"/>
+      <c r="U53" s="32"/>
+      <c r="V53" s="32"/>
+      <c r="W53" s="33"/>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A54" s="31"/>
+      <c r="B54" s="32"/>
+      <c r="C54" s="32"/>
+      <c r="D54" s="32"/>
+      <c r="E54" s="32"/>
+      <c r="F54" s="32"/>
+      <c r="G54" s="32"/>
+      <c r="H54" s="32"/>
+      <c r="I54" s="32"/>
+      <c r="J54" s="32"/>
+      <c r="K54" s="32"/>
+      <c r="L54" s="32"/>
+      <c r="M54" s="32"/>
+      <c r="N54" s="32"/>
+      <c r="O54" s="32"/>
+      <c r="P54" s="32"/>
+      <c r="Q54" s="32"/>
+      <c r="R54" s="32"/>
+      <c r="S54" s="32"/>
+      <c r="T54" s="32"/>
+      <c r="U54" s="32"/>
+      <c r="V54" s="32"/>
+      <c r="W54" s="33"/>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A55" s="31"/>
+      <c r="B55" s="32"/>
+      <c r="C55" s="32"/>
+      <c r="D55" s="32"/>
+      <c r="E55" s="32"/>
+      <c r="F55" s="32"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="32"/>
+      <c r="I55" s="32"/>
+      <c r="J55" s="32"/>
+      <c r="K55" s="32"/>
+      <c r="L55" s="32"/>
+      <c r="M55" s="32"/>
+      <c r="N55" s="32"/>
+      <c r="O55" s="32"/>
+      <c r="P55" s="32"/>
+      <c r="Q55" s="32"/>
+      <c r="R55" s="32"/>
+      <c r="S55" s="32"/>
+      <c r="T55" s="32"/>
+      <c r="U55" s="32"/>
+      <c r="V55" s="32"/>
+      <c r="W55" s="33"/>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A56" s="31"/>
+      <c r="B56" s="32"/>
+      <c r="C56" s="32"/>
+      <c r="D56" s="32"/>
+      <c r="E56" s="32"/>
+      <c r="F56" s="32"/>
+      <c r="G56" s="32"/>
+      <c r="H56" s="32"/>
+      <c r="I56" s="32"/>
+      <c r="J56" s="32"/>
+      <c r="K56" s="32"/>
+      <c r="L56" s="32"/>
+      <c r="M56" s="32"/>
+      <c r="N56" s="32"/>
+      <c r="O56" s="32"/>
+      <c r="P56" s="32"/>
+      <c r="Q56" s="32"/>
+      <c r="R56" s="32"/>
+      <c r="S56" s="32"/>
+      <c r="T56" s="32"/>
+      <c r="U56" s="32"/>
+      <c r="V56" s="32"/>
+      <c r="W56" s="33"/>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A57" s="31"/>
+      <c r="B57" s="32"/>
+      <c r="C57" s="32"/>
+      <c r="D57" s="32"/>
+      <c r="E57" s="32"/>
+      <c r="F57" s="32"/>
+      <c r="G57" s="32"/>
+      <c r="H57" s="32"/>
+      <c r="I57" s="32"/>
+      <c r="J57" s="32"/>
+      <c r="K57" s="32"/>
+      <c r="L57" s="32"/>
+      <c r="M57" s="32"/>
+      <c r="N57" s="32"/>
+      <c r="O57" s="32"/>
+      <c r="P57" s="32"/>
+      <c r="Q57" s="32"/>
+      <c r="R57" s="32"/>
+      <c r="S57" s="32"/>
+      <c r="T57" s="32"/>
+      <c r="U57" s="32"/>
+      <c r="V57" s="32"/>
+      <c r="W57" s="33"/>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A58" s="31"/>
+      <c r="B58" s="32"/>
+      <c r="C58" s="32"/>
+      <c r="D58" s="32"/>
+      <c r="E58" s="32"/>
+      <c r="F58" s="32"/>
+      <c r="G58" s="32"/>
+      <c r="H58" s="32"/>
+      <c r="I58" s="32"/>
+      <c r="J58" s="32"/>
+      <c r="K58" s="32"/>
+      <c r="L58" s="32"/>
+      <c r="M58" s="32"/>
+      <c r="N58" s="32"/>
+      <c r="O58" s="32"/>
+      <c r="P58" s="32"/>
+      <c r="Q58" s="32"/>
+      <c r="R58" s="32"/>
+      <c r="S58" s="32"/>
+      <c r="T58" s="32"/>
+      <c r="U58" s="32"/>
+      <c r="V58" s="32"/>
+      <c r="W58" s="33"/>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A59" s="31"/>
+      <c r="B59" s="32"/>
+      <c r="C59" s="32"/>
+      <c r="D59" s="32"/>
+      <c r="E59" s="32"/>
+      <c r="F59" s="32"/>
+      <c r="G59" s="32"/>
+      <c r="H59" s="32"/>
+      <c r="I59" s="32"/>
+      <c r="J59" s="32"/>
+      <c r="K59" s="32"/>
+      <c r="L59" s="32"/>
+      <c r="M59" s="32"/>
+      <c r="N59" s="32"/>
+      <c r="O59" s="32"/>
+      <c r="P59" s="32"/>
+      <c r="Q59" s="32"/>
+      <c r="R59" s="32"/>
+      <c r="S59" s="32"/>
+      <c r="T59" s="32"/>
+      <c r="U59" s="32"/>
+      <c r="V59" s="32"/>
+      <c r="W59" s="33"/>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A60" s="31"/>
+      <c r="B60" s="32"/>
+      <c r="C60" s="32"/>
+      <c r="D60" s="32"/>
+      <c r="E60" s="32"/>
+      <c r="F60" s="32"/>
+      <c r="G60" s="32"/>
+      <c r="H60" s="32"/>
+      <c r="I60" s="32"/>
+      <c r="J60" s="32"/>
+      <c r="K60" s="32"/>
+      <c r="L60" s="32"/>
+      <c r="M60" s="32"/>
+      <c r="N60" s="32"/>
+      <c r="O60" s="32"/>
+      <c r="P60" s="32"/>
+      <c r="Q60" s="32"/>
+      <c r="R60" s="32"/>
+      <c r="S60" s="32"/>
+      <c r="T60" s="32"/>
+      <c r="U60" s="32"/>
+      <c r="V60" s="32"/>
+      <c r="W60" s="33"/>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A61" s="31"/>
+      <c r="B61" s="32"/>
+      <c r="C61" s="32"/>
+      <c r="D61" s="32"/>
+      <c r="E61" s="32"/>
+      <c r="F61" s="32"/>
+      <c r="G61" s="32"/>
+      <c r="H61" s="32"/>
+      <c r="I61" s="32"/>
+      <c r="J61" s="32"/>
+      <c r="K61" s="32"/>
+      <c r="L61" s="32"/>
+      <c r="M61" s="32"/>
+      <c r="N61" s="32"/>
+      <c r="O61" s="32"/>
+      <c r="P61" s="32"/>
+      <c r="Q61" s="32"/>
+      <c r="R61" s="32"/>
+      <c r="S61" s="32"/>
+      <c r="T61" s="32"/>
+      <c r="U61" s="32"/>
+      <c r="V61" s="32"/>
+      <c r="W61" s="33"/>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A62" s="31"/>
+      <c r="B62" s="32"/>
+      <c r="C62" s="32"/>
+      <c r="D62" s="32"/>
+      <c r="E62" s="32"/>
+      <c r="F62" s="32"/>
+      <c r="G62" s="32"/>
+      <c r="H62" s="32"/>
+      <c r="I62" s="32"/>
+      <c r="J62" s="32"/>
+      <c r="K62" s="32"/>
+      <c r="L62" s="32"/>
+      <c r="M62" s="32"/>
+      <c r="N62" s="32"/>
+      <c r="O62" s="32"/>
+      <c r="P62" s="32"/>
+      <c r="Q62" s="32"/>
+      <c r="R62" s="32"/>
+      <c r="S62" s="32"/>
+      <c r="T62" s="32"/>
+      <c r="U62" s="32"/>
+      <c r="V62" s="32"/>
+      <c r="W62" s="33"/>
+    </row>
+    <row r="63" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="34"/>
+      <c r="B63" s="35"/>
+      <c r="C63" s="35"/>
+      <c r="D63" s="35"/>
+      <c r="E63" s="35"/>
+      <c r="F63" s="35"/>
+      <c r="G63" s="35"/>
+      <c r="H63" s="35"/>
+      <c r="I63" s="35"/>
+      <c r="J63" s="35"/>
+      <c r="K63" s="35"/>
+      <c r="L63" s="35"/>
+      <c r="M63" s="35"/>
+      <c r="N63" s="35"/>
+      <c r="O63" s="35"/>
+      <c r="P63" s="35"/>
+      <c r="Q63" s="35"/>
+      <c r="R63" s="35"/>
+      <c r="S63" s="35"/>
+      <c r="T63" s="35"/>
+      <c r="U63" s="35"/>
+      <c r="V63" s="35"/>
+      <c r="W63" s="36"/>
+    </row>
+    <row r="64" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="37"/>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A65" s="38" t="s">
+        <v>551</v>
+      </c>
+      <c r="B65" s="39"/>
+      <c r="C65" s="39"/>
+      <c r="D65" s="39"/>
+      <c r="E65" s="39"/>
+      <c r="F65" s="39"/>
+      <c r="G65" s="39"/>
+      <c r="H65" s="39"/>
+      <c r="I65" s="39"/>
+      <c r="J65" s="39"/>
+      <c r="K65" s="39"/>
+      <c r="L65" s="39"/>
+      <c r="M65" s="39"/>
+      <c r="N65" s="39"/>
+      <c r="O65" s="39"/>
+      <c r="P65" s="39"/>
+      <c r="Q65" s="39"/>
+      <c r="R65" s="39"/>
+      <c r="S65" s="39"/>
+      <c r="T65" s="39"/>
+      <c r="U65" s="39"/>
+      <c r="V65" s="39"/>
+      <c r="W65" s="40"/>
+    </row>
+    <row r="66" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="41"/>
+      <c r="B66" s="42"/>
+      <c r="C66" s="42"/>
+      <c r="D66" s="42"/>
+      <c r="E66" s="42"/>
+      <c r="F66" s="42"/>
+      <c r="G66" s="42"/>
+      <c r="H66" s="42"/>
+      <c r="I66" s="42"/>
+      <c r="J66" s="42"/>
+      <c r="K66" s="42"/>
+      <c r="L66" s="42"/>
+      <c r="M66" s="42"/>
+      <c r="N66" s="42"/>
+      <c r="O66" s="42"/>
+      <c r="P66" s="42"/>
+      <c r="Q66" s="42"/>
+      <c r="R66" s="42"/>
+      <c r="S66" s="42"/>
+      <c r="T66" s="42"/>
+      <c r="U66" s="42"/>
+      <c r="V66" s="42"/>
+      <c r="W66" s="43"/>
+    </row>
+    <row r="67" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="44" t="s">
         <v>548</v>
       </c>
-      <c r="M17" s="25"/>
-      <c r="N17" s="25"/>
-      <c r="O17" s="25"/>
-      <c r="P17" s="25"/>
-      <c r="Q17" s="25"/>
-      <c r="R17" s="25"/>
-      <c r="S17" s="25"/>
-      <c r="T17" s="25"/>
-      <c r="U17" s="25"/>
-      <c r="V17" s="25"/>
-      <c r="W17" s="26"/>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A18" s="27"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="28"/>
-      <c r="K18" s="29"/>
-      <c r="L18" s="30"/>
-      <c r="M18" s="31"/>
-      <c r="N18" s="31"/>
-      <c r="O18" s="31"/>
-      <c r="P18" s="31"/>
-      <c r="Q18" s="31"/>
-      <c r="R18" s="31"/>
-      <c r="S18" s="31"/>
-      <c r="T18" s="31"/>
-      <c r="U18" s="31"/>
-      <c r="V18" s="31"/>
-      <c r="W18" s="32"/>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A19" s="27"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="29"/>
-      <c r="L19" s="30"/>
-      <c r="M19" s="31"/>
-      <c r="N19" s="31"/>
-      <c r="O19" s="31"/>
-      <c r="P19" s="31"/>
-      <c r="Q19" s="31"/>
-      <c r="R19" s="31"/>
-      <c r="S19" s="31"/>
-      <c r="T19" s="31"/>
-      <c r="U19" s="31"/>
-      <c r="V19" s="31"/>
-      <c r="W19" s="32"/>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A20" s="27"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="31"/>
-      <c r="N20" s="31"/>
-      <c r="O20" s="31"/>
-      <c r="P20" s="31"/>
-      <c r="Q20" s="31"/>
-      <c r="R20" s="31"/>
-      <c r="S20" s="31"/>
-      <c r="T20" s="31"/>
-      <c r="U20" s="31"/>
-      <c r="V20" s="31"/>
-      <c r="W20" s="32"/>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A21" s="27"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="28"/>
-      <c r="J21" s="28"/>
-      <c r="K21" s="29"/>
-      <c r="L21" s="30"/>
-      <c r="M21" s="31"/>
-      <c r="N21" s="31"/>
-      <c r="O21" s="31"/>
-      <c r="P21" s="31"/>
-      <c r="Q21" s="31"/>
-      <c r="R21" s="31"/>
-      <c r="S21" s="31"/>
-      <c r="T21" s="31"/>
-      <c r="U21" s="31"/>
-      <c r="V21" s="31"/>
-      <c r="W21" s="32"/>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A22" s="27"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="28"/>
-      <c r="K22" s="29"/>
-      <c r="L22" s="30"/>
-      <c r="M22" s="31"/>
-      <c r="N22" s="31"/>
-      <c r="O22" s="31"/>
-      <c r="P22" s="31"/>
-      <c r="Q22" s="31"/>
-      <c r="R22" s="31"/>
-      <c r="S22" s="31"/>
-      <c r="T22" s="31"/>
-      <c r="U22" s="31"/>
-      <c r="V22" s="31"/>
-      <c r="W22" s="32"/>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A23" s="27"/>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="29"/>
-      <c r="L23" s="30"/>
-      <c r="M23" s="31"/>
-      <c r="N23" s="31"/>
-      <c r="O23" s="31"/>
-      <c r="P23" s="31"/>
-      <c r="Q23" s="31"/>
-      <c r="R23" s="31"/>
-      <c r="S23" s="31"/>
-      <c r="T23" s="31"/>
-      <c r="U23" s="31"/>
-      <c r="V23" s="31"/>
-      <c r="W23" s="32"/>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A24" s="27"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="28"/>
-      <c r="K24" s="29"/>
-      <c r="L24" s="30"/>
-      <c r="M24" s="31"/>
-      <c r="N24" s="31"/>
-      <c r="O24" s="31"/>
-      <c r="P24" s="31"/>
-      <c r="Q24" s="31"/>
-      <c r="R24" s="31"/>
-      <c r="S24" s="31"/>
-      <c r="T24" s="31"/>
-      <c r="U24" s="31"/>
-      <c r="V24" s="31"/>
-      <c r="W24" s="32"/>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A25" s="27"/>
-      <c r="B25" s="28"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="28"/>
-      <c r="K25" s="29"/>
-      <c r="L25" s="30"/>
-      <c r="M25" s="31"/>
-      <c r="N25" s="31"/>
-      <c r="O25" s="31"/>
-      <c r="P25" s="31"/>
-      <c r="Q25" s="31"/>
-      <c r="R25" s="31"/>
-      <c r="S25" s="31"/>
-      <c r="T25" s="31"/>
-      <c r="U25" s="31"/>
-      <c r="V25" s="31"/>
-      <c r="W25" s="32"/>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A26" s="27"/>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="30"/>
-      <c r="M26" s="31"/>
-      <c r="N26" s="31"/>
-      <c r="O26" s="31"/>
-      <c r="P26" s="31"/>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="31"/>
-      <c r="S26" s="31"/>
-      <c r="T26" s="31"/>
-      <c r="U26" s="31"/>
-      <c r="V26" s="31"/>
-      <c r="W26" s="32"/>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A27" s="27"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="28"/>
-      <c r="J27" s="28"/>
-      <c r="K27" s="29"/>
-      <c r="L27" s="30"/>
-      <c r="M27" s="31"/>
-      <c r="N27" s="31"/>
-      <c r="O27" s="31"/>
-      <c r="P27" s="31"/>
-      <c r="Q27" s="31"/>
-      <c r="R27" s="31"/>
-      <c r="S27" s="31"/>
-      <c r="T27" s="31"/>
-      <c r="U27" s="31"/>
-      <c r="V27" s="31"/>
-      <c r="W27" s="32"/>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A28" s="27"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="28"/>
-      <c r="J28" s="28"/>
-      <c r="K28" s="29"/>
-      <c r="L28" s="30"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
-      <c r="T28" s="31"/>
-      <c r="U28" s="31"/>
-      <c r="V28" s="31"/>
-      <c r="W28" s="32"/>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A29" s="27"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28"/>
-      <c r="J29" s="28"/>
-      <c r="K29" s="29"/>
-      <c r="L29" s="30"/>
-      <c r="M29" s="31"/>
-      <c r="N29" s="31"/>
-      <c r="O29" s="31"/>
-      <c r="P29" s="31"/>
-      <c r="Q29" s="31"/>
-      <c r="R29" s="31"/>
-      <c r="S29" s="31"/>
-      <c r="T29" s="31"/>
-      <c r="U29" s="31"/>
-      <c r="V29" s="31"/>
-      <c r="W29" s="32"/>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A30" s="27"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="28"/>
-      <c r="J30" s="28"/>
-      <c r="K30" s="29"/>
-      <c r="L30" s="30"/>
-      <c r="M30" s="31"/>
-      <c r="N30" s="31"/>
-      <c r="O30" s="31"/>
-      <c r="P30" s="31"/>
-      <c r="Q30" s="31"/>
-      <c r="R30" s="31"/>
-      <c r="S30" s="31"/>
-      <c r="T30" s="31"/>
-      <c r="U30" s="31"/>
-      <c r="V30" s="31"/>
-      <c r="W30" s="32"/>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A31" s="27"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="28"/>
-      <c r="J31" s="28"/>
-      <c r="K31" s="29"/>
-      <c r="L31" s="30"/>
-      <c r="M31" s="31"/>
-      <c r="N31" s="31"/>
-      <c r="O31" s="31"/>
-      <c r="P31" s="31"/>
-      <c r="Q31" s="31"/>
-      <c r="R31" s="31"/>
-      <c r="S31" s="31"/>
-      <c r="T31" s="31"/>
-      <c r="U31" s="31"/>
-      <c r="V31" s="31"/>
-      <c r="W31" s="32"/>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A32" s="27"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="30"/>
-      <c r="M32" s="31"/>
-      <c r="N32" s="31"/>
-      <c r="O32" s="31"/>
-      <c r="P32" s="31"/>
-      <c r="Q32" s="31"/>
-      <c r="R32" s="31"/>
-      <c r="S32" s="31"/>
-      <c r="T32" s="31"/>
-      <c r="U32" s="31"/>
-      <c r="V32" s="31"/>
-      <c r="W32" s="32"/>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A33" s="27"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="28"/>
-      <c r="J33" s="28"/>
-      <c r="K33" s="29"/>
-      <c r="L33" s="30"/>
-      <c r="M33" s="31"/>
-      <c r="N33" s="31"/>
-      <c r="O33" s="31"/>
-      <c r="P33" s="31"/>
-      <c r="Q33" s="31"/>
-      <c r="R33" s="31"/>
-      <c r="S33" s="31"/>
-      <c r="T33" s="31"/>
-      <c r="U33" s="31"/>
-      <c r="V33" s="31"/>
-      <c r="W33" s="32"/>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A34" s="27"/>
-      <c r="B34" s="28"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="28"/>
-      <c r="J34" s="28"/>
-      <c r="K34" s="29"/>
-      <c r="L34" s="30"/>
-      <c r="M34" s="31"/>
-      <c r="N34" s="31"/>
-      <c r="O34" s="31"/>
-      <c r="P34" s="31"/>
-      <c r="Q34" s="31"/>
-      <c r="R34" s="31"/>
-      <c r="S34" s="31"/>
-      <c r="T34" s="31"/>
-      <c r="U34" s="31"/>
-      <c r="V34" s="31"/>
-      <c r="W34" s="32"/>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A35" s="27"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="28"/>
-      <c r="J35" s="28"/>
-      <c r="K35" s="29"/>
-      <c r="L35" s="30"/>
-      <c r="M35" s="31"/>
-      <c r="N35" s="31"/>
-      <c r="O35" s="31"/>
-      <c r="P35" s="31"/>
-      <c r="Q35" s="31"/>
-      <c r="R35" s="31"/>
-      <c r="S35" s="31"/>
-      <c r="T35" s="31"/>
-      <c r="U35" s="31"/>
-      <c r="V35" s="31"/>
-      <c r="W35" s="32"/>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A36" s="27"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="28"/>
-      <c r="J36" s="28"/>
-      <c r="K36" s="29"/>
-      <c r="L36" s="30"/>
-      <c r="M36" s="31"/>
-      <c r="N36" s="31"/>
-      <c r="O36" s="31"/>
-      <c r="P36" s="31"/>
-      <c r="Q36" s="31"/>
-      <c r="R36" s="31"/>
-      <c r="S36" s="31"/>
-      <c r="T36" s="31"/>
-      <c r="U36" s="31"/>
-      <c r="V36" s="31"/>
-      <c r="W36" s="32"/>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A37" s="27"/>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28"/>
-      <c r="J37" s="28"/>
-      <c r="K37" s="29"/>
-      <c r="L37" s="30"/>
-      <c r="M37" s="31"/>
-      <c r="N37" s="31"/>
-      <c r="O37" s="31"/>
-      <c r="P37" s="31"/>
-      <c r="Q37" s="31"/>
-      <c r="R37" s="31"/>
-      <c r="S37" s="31"/>
-      <c r="T37" s="31"/>
-      <c r="U37" s="31"/>
-      <c r="V37" s="31"/>
-      <c r="W37" s="32"/>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A38" s="27"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="28"/>
-      <c r="J38" s="28"/>
-      <c r="K38" s="29"/>
-      <c r="L38" s="30"/>
-      <c r="M38" s="31"/>
-      <c r="N38" s="31"/>
-      <c r="O38" s="31"/>
-      <c r="P38" s="31"/>
-      <c r="Q38" s="31"/>
-      <c r="R38" s="31"/>
-      <c r="S38" s="31"/>
-      <c r="T38" s="31"/>
-      <c r="U38" s="31"/>
-      <c r="V38" s="31"/>
-      <c r="W38" s="32"/>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A39" s="27"/>
-      <c r="B39" s="28"/>
-      <c r="C39" s="28"/>
-      <c r="D39" s="28"/>
-      <c r="E39" s="28"/>
-      <c r="F39" s="28"/>
-      <c r="G39" s="28"/>
-      <c r="H39" s="28"/>
-      <c r="I39" s="28"/>
-      <c r="J39" s="28"/>
-      <c r="K39" s="29"/>
-      <c r="L39" s="30"/>
-      <c r="M39" s="31"/>
-      <c r="N39" s="31"/>
-      <c r="O39" s="31"/>
-      <c r="P39" s="31"/>
-      <c r="Q39" s="31"/>
-      <c r="R39" s="31"/>
-      <c r="S39" s="31"/>
-      <c r="T39" s="31"/>
-      <c r="U39" s="31"/>
-      <c r="V39" s="31"/>
-      <c r="W39" s="32"/>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A40" s="27"/>
-      <c r="B40" s="28"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="28"/>
-      <c r="J40" s="28"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="30"/>
-      <c r="M40" s="31"/>
-      <c r="N40" s="31"/>
-      <c r="O40" s="31"/>
-      <c r="P40" s="31"/>
-      <c r="Q40" s="31"/>
-      <c r="R40" s="31"/>
-      <c r="S40" s="31"/>
-      <c r="T40" s="31"/>
-      <c r="U40" s="31"/>
-      <c r="V40" s="31"/>
-      <c r="W40" s="32"/>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A41" s="27"/>
-      <c r="B41" s="28"/>
-      <c r="C41" s="28"/>
-      <c r="D41" s="28"/>
-      <c r="E41" s="28"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="28"/>
-      <c r="H41" s="28"/>
-      <c r="I41" s="28"/>
-      <c r="J41" s="28"/>
-      <c r="K41" s="29"/>
-      <c r="L41" s="30"/>
-      <c r="M41" s="31"/>
-      <c r="N41" s="31"/>
-      <c r="O41" s="31"/>
-      <c r="P41" s="31"/>
-      <c r="Q41" s="31"/>
-      <c r="R41" s="31"/>
-      <c r="S41" s="31"/>
-      <c r="T41" s="31"/>
-      <c r="U41" s="31"/>
-      <c r="V41" s="31"/>
-      <c r="W41" s="32"/>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A42" s="27"/>
-      <c r="B42" s="28"/>
-      <c r="C42" s="28"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="28"/>
-      <c r="G42" s="28"/>
-      <c r="H42" s="28"/>
-      <c r="I42" s="28"/>
-      <c r="J42" s="28"/>
-      <c r="K42" s="29"/>
-      <c r="L42" s="30"/>
-      <c r="M42" s="31"/>
-      <c r="N42" s="31"/>
-      <c r="O42" s="31"/>
-      <c r="P42" s="31"/>
-      <c r="Q42" s="31"/>
-      <c r="R42" s="31"/>
-      <c r="S42" s="31"/>
-      <c r="T42" s="31"/>
-      <c r="U42" s="31"/>
-      <c r="V42" s="31"/>
-      <c r="W42" s="32"/>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A43" s="27"/>
-      <c r="B43" s="28"/>
-      <c r="C43" s="28"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="28"/>
-      <c r="I43" s="28"/>
-      <c r="J43" s="28"/>
-      <c r="K43" s="29"/>
-      <c r="L43" s="30"/>
-      <c r="M43" s="31"/>
-      <c r="N43" s="31"/>
-      <c r="O43" s="31"/>
-      <c r="P43" s="31"/>
-      <c r="Q43" s="31"/>
-      <c r="R43" s="31"/>
-      <c r="S43" s="31"/>
-      <c r="T43" s="31"/>
-      <c r="U43" s="31"/>
-      <c r="V43" s="31"/>
-      <c r="W43" s="32"/>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A44" s="27"/>
-      <c r="B44" s="28"/>
-      <c r="C44" s="28"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="28"/>
-      <c r="H44" s="28"/>
-      <c r="I44" s="28"/>
-      <c r="J44" s="28"/>
-      <c r="K44" s="29"/>
-      <c r="L44" s="30"/>
-      <c r="M44" s="31"/>
-      <c r="N44" s="31"/>
-      <c r="O44" s="31"/>
-      <c r="P44" s="31"/>
-      <c r="Q44" s="31"/>
-      <c r="R44" s="31"/>
-      <c r="S44" s="31"/>
-      <c r="T44" s="31"/>
-      <c r="U44" s="31"/>
-      <c r="V44" s="31"/>
-      <c r="W44" s="32"/>
-    </row>
-    <row r="45" spans="1:23" ht="63" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="27"/>
-      <c r="B45" s="28"/>
-      <c r="C45" s="28"/>
-      <c r="D45" s="28"/>
-      <c r="E45" s="28"/>
-      <c r="F45" s="28"/>
-      <c r="G45" s="28"/>
-      <c r="H45" s="28"/>
-      <c r="I45" s="28"/>
-      <c r="J45" s="28"/>
-      <c r="K45" s="29"/>
-      <c r="L45" s="30"/>
-      <c r="M45" s="31"/>
-      <c r="N45" s="31"/>
-      <c r="O45" s="31"/>
-      <c r="P45" s="31"/>
-      <c r="Q45" s="31"/>
-      <c r="R45" s="31"/>
-      <c r="S45" s="31"/>
-      <c r="T45" s="31"/>
-      <c r="U45" s="31"/>
-      <c r="V45" s="31"/>
-      <c r="W45" s="32"/>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A46" s="27"/>
-      <c r="B46" s="28"/>
-      <c r="C46" s="28"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="28"/>
-      <c r="H46" s="28"/>
-      <c r="I46" s="28"/>
-      <c r="J46" s="28"/>
-      <c r="K46" s="29"/>
-      <c r="L46" s="30"/>
-      <c r="M46" s="31"/>
-      <c r="N46" s="31"/>
-      <c r="O46" s="31"/>
-      <c r="P46" s="31"/>
-      <c r="Q46" s="31"/>
-      <c r="R46" s="31"/>
-      <c r="S46" s="31"/>
-      <c r="T46" s="31"/>
-      <c r="U46" s="31"/>
-      <c r="V46" s="31"/>
-      <c r="W46" s="32"/>
-    </row>
-    <row r="47" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="33"/>
-      <c r="B47" s="34"/>
-      <c r="C47" s="34"/>
-      <c r="D47" s="34"/>
-      <c r="E47" s="34"/>
-      <c r="F47" s="34"/>
-      <c r="G47" s="34"/>
-      <c r="H47" s="34"/>
-      <c r="I47" s="34"/>
-      <c r="J47" s="34"/>
-      <c r="K47" s="35"/>
-      <c r="L47" s="36"/>
-      <c r="M47" s="37"/>
-      <c r="N47" s="37"/>
-      <c r="O47" s="37"/>
-      <c r="P47" s="37"/>
-      <c r="Q47" s="37"/>
-      <c r="R47" s="37"/>
-      <c r="S47" s="37"/>
-      <c r="T47" s="37"/>
-      <c r="U47" s="37"/>
-      <c r="V47" s="37"/>
-      <c r="W47" s="38"/>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A48" s="39" t="s">
-        <v>549</v>
-      </c>
-      <c r="B48" s="40"/>
-      <c r="C48" s="40"/>
-      <c r="D48" s="40"/>
-      <c r="E48" s="40"/>
-      <c r="F48" s="40"/>
-      <c r="G48" s="40"/>
-      <c r="H48" s="40"/>
-      <c r="I48" s="40"/>
-      <c r="J48" s="40"/>
-      <c r="K48" s="40"/>
-      <c r="L48" s="40"/>
-      <c r="M48" s="40"/>
-      <c r="N48" s="40"/>
-      <c r="O48" s="40"/>
-      <c r="P48" s="40"/>
-      <c r="Q48" s="40"/>
-      <c r="R48" s="40"/>
-      <c r="S48" s="40"/>
-      <c r="T48" s="40"/>
-      <c r="U48" s="40"/>
-      <c r="V48" s="40"/>
-      <c r="W48" s="41"/>
-    </row>
-    <row r="49" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="42"/>
-      <c r="B49" s="43"/>
-      <c r="C49" s="43"/>
-      <c r="D49" s="43"/>
-      <c r="E49" s="43"/>
-      <c r="F49" s="43"/>
-      <c r="G49" s="43"/>
-      <c r="H49" s="43"/>
-      <c r="I49" s="43"/>
-      <c r="J49" s="43"/>
-      <c r="K49" s="43"/>
-      <c r="L49" s="43"/>
-      <c r="M49" s="43"/>
-      <c r="N49" s="43"/>
-      <c r="O49" s="43"/>
-      <c r="P49" s="43"/>
-      <c r="Q49" s="43"/>
-      <c r="R49" s="43"/>
-      <c r="S49" s="43"/>
-      <c r="T49" s="43"/>
-      <c r="U49" s="43"/>
-      <c r="V49" s="43"/>
-      <c r="W49" s="44"/>
-    </row>
-    <row r="50" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="45" t="s">
-        <v>550</v>
-      </c>
-      <c r="B50" s="46"/>
-      <c r="C50" s="46"/>
-      <c r="D50" s="46"/>
-      <c r="E50" s="46"/>
-      <c r="F50" s="46"/>
-      <c r="G50" s="46"/>
-      <c r="H50" s="46"/>
-      <c r="I50" s="46"/>
-      <c r="J50" s="46"/>
-      <c r="K50" s="46"/>
-      <c r="L50" s="46"/>
-      <c r="M50" s="46"/>
-      <c r="N50" s="46"/>
-      <c r="O50" s="46"/>
-      <c r="P50" s="46"/>
-      <c r="Q50" s="46"/>
-      <c r="R50" s="46"/>
-      <c r="S50" s="46"/>
-      <c r="T50" s="46"/>
-      <c r="U50" s="46"/>
-      <c r="V50" s="46"/>
-      <c r="W50" s="47"/>
-    </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="S51" s="48" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A59" s="49"/>
-    </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A60" s="50"/>
-    </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A61" s="50"/>
-    </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A62" s="50"/>
-    </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A63" s="50"/>
-    </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A64" s="50"/>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="50"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="50"/>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="50"/>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="50"/>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="50"/>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="50"/>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="50"/>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="50"/>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="50"/>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="50"/>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="50"/>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="50"/>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="50"/>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="50"/>
+      <c r="B67" s="45"/>
+      <c r="C67" s="45"/>
+      <c r="D67" s="45"/>
+      <c r="E67" s="45"/>
+      <c r="F67" s="45"/>
+      <c r="G67" s="45"/>
+      <c r="H67" s="45"/>
+      <c r="I67" s="45"/>
+      <c r="J67" s="45"/>
+      <c r="K67" s="45"/>
+      <c r="L67" s="45"/>
+      <c r="M67" s="45"/>
+      <c r="N67" s="45"/>
+      <c r="O67" s="45"/>
+      <c r="P67" s="45"/>
+      <c r="Q67" s="45"/>
+      <c r="R67" s="45"/>
+      <c r="S67" s="45"/>
+      <c r="T67" s="45"/>
+      <c r="U67" s="45"/>
+      <c r="V67" s="45"/>
+      <c r="W67" s="46"/>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A68" s="37"/>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A69" s="37"/>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A70" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A48:W49"/>
-    <mergeCell ref="A50:W50"/>
+    <mergeCell ref="A65:W66"/>
+    <mergeCell ref="A67:W67"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A13:W14"/>
-    <mergeCell ref="A16:W16"/>
-    <mergeCell ref="A17:K47"/>
-    <mergeCell ref="L17:W47"/>
+    <mergeCell ref="A4:W4"/>
+    <mergeCell ref="A6:W7"/>
+    <mergeCell ref="A9:W9"/>
+    <mergeCell ref="A10:W63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:V15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -3735,7 +4895,7 @@
     <col min="11" max="22" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -3803,7 +4963,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -3871,7 +5031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -3939,7 +5099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -4007,7 +5167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -4075,7 +5235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -4143,7 +5303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -4211,7 +5371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -4279,7 +5439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -4347,7 +5507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -4415,7 +5575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -4483,7 +5643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -4551,7 +5711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -4619,7 +5779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -4687,7 +5847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -4764,7 +5924,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:Y15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -4775,7 +5935,7 @@
     <col min="11" max="25" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -4852,7 +6012,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -4929,7 +6089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -5006,7 +6166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -5083,7 +6243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -5160,7 +6320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -5237,7 +6397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -5314,7 +6474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -5391,7 +6551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -5468,7 +6628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -5545,7 +6705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -5622,7 +6782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -5699,7 +6859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -5776,7 +6936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -5853,7 +7013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -5939,7 +7099,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -5949,7 +7109,7 @@
     <col min="8" max="10" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -5981,7 +7141,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -6013,7 +7173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -6045,7 +7205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -6077,7 +7237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -6109,7 +7269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -6141,7 +7301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -6173,7 +7333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -6205,7 +7365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -6237,7 +7397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -6269,7 +7429,7 @@
         <v>2.6667000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -6301,7 +7461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -6333,7 +7493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -6365,7 +7525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -6397,7 +7557,7 @@
         <v>1.0667</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -6438,7 +7598,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:S15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -6449,7 +7609,7 @@
     <col min="11" max="19" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -6508,7 +7668,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -6567,7 +7727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -6626,7 +7786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -6685,7 +7845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -6744,7 +7904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -6803,7 +7963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -6862,7 +8022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -6921,7 +8081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -6980,7 +8140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -7039,7 +8199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -7098,7 +8258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -7157,7 +8317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -7216,7 +8376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -7275,7 +8435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -7343,7 +8503,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:Y15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -7354,7 +8514,7 @@
     <col min="11" max="25" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -7431,7 +8591,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -7508,7 +8668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -7585,7 +8745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -7662,7 +8822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -7739,7 +8899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -7816,7 +8976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -7893,7 +9053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -7970,7 +9130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -8047,7 +9207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -8124,7 +9284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -8201,7 +9361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -8278,7 +9438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -8355,7 +9515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -8432,7 +9592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -8518,7 +9678,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:AE15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -8529,7 +9689,7 @@
     <col min="11" max="31" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -8624,7 +9784,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -8719,7 +9879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -8814,7 +9974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -8909,7 +10069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -9004,7 +10164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -9099,7 +10259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -9194,7 +10354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -9289,7 +10449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -9384,7 +10544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -9479,7 +10639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -9574,7 +10734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -9669,7 +10829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -9764,7 +10924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -9859,7 +11019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -9963,7 +11123,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:V15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -9974,7 +11134,7 @@
     <col min="11" max="22" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -10042,7 +11202,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -10110,7 +11270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -10178,7 +11338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -10246,7 +11406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -10314,7 +11474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -10382,7 +11542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -10450,7 +11610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -10518,7 +11678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -10586,7 +11746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -10654,7 +11814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -10722,7 +11882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -10790,7 +11950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -10858,7 +12018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -10926,7 +12086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -11003,7 +12163,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -11013,7 +12173,7 @@
     <col min="8" max="10" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -11045,7 +12205,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -11077,7 +12237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -11109,7 +12269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -11141,7 +12301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -11173,7 +12333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -11205,7 +12365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -11237,7 +12397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -11269,7 +12429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -11301,7 +12461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -11333,7 +12493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -11365,7 +12525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -11397,7 +12557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -11429,7 +12589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -11461,7 +12621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -11502,14 +12662,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C113"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="130" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -11519,8 +12679,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -11530,8 +12690,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="10"/>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="11"/>
       <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
@@ -11539,8 +12699,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="10"/>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="11"/>
       <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
@@ -11548,8 +12708,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="10"/>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="11"/>
       <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
@@ -11557,8 +12717,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="11"/>
       <c r="B6" s="3" t="s">
         <v>12</v>
       </c>
@@ -11566,8 +12726,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="10"/>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="11"/>
       <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
@@ -11575,8 +12735,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="11"/>
       <c r="B8" s="3" t="s">
         <v>16</v>
       </c>
@@ -11584,8 +12744,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="10"/>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="11"/>
       <c r="B9" s="3" t="s">
         <v>18</v>
       </c>
@@ -11593,8 +12753,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="10"/>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="11"/>
       <c r="B10" s="3" t="s">
         <v>20</v>
       </c>
@@ -11602,8 +12762,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="10"/>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="11"/>
       <c r="B11" s="3" t="s">
         <v>22</v>
       </c>
@@ -11611,8 +12771,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="10"/>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="11"/>
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
@@ -11620,8 +12780,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="10"/>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="11"/>
       <c r="B13" s="3" t="s">
         <v>26</v>
       </c>
@@ -11629,8 +12789,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="10"/>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="11"/>
       <c r="B14" s="3" t="s">
         <v>28</v>
       </c>
@@ -11638,8 +12798,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="10"/>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="11"/>
       <c r="B15" s="3" t="s">
         <v>30</v>
       </c>
@@ -11647,8 +12807,8 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="11"/>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="12"/>
       <c r="B16" s="5" t="s">
         <v>32</v>
       </c>
@@ -11656,20 +12816,20 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
+    <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-    </row>
-    <row r="18" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+    </row>
+    <row r="18" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="9" t="s">
         <v>35</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -11679,8 +12839,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="14"/>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="9"/>
       <c r="B20" s="3" t="s">
         <v>38</v>
       </c>
@@ -11688,8 +12848,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="9"/>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="10"/>
       <c r="B21" s="5" t="s">
         <v>40</v>
       </c>
@@ -11697,8 +12857,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="11" t="s">
         <v>42</v>
       </c>
       <c r="B22" s="3" t="s">
@@ -11708,8 +12868,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="10"/>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="11"/>
       <c r="B23" s="3" t="s">
         <v>45</v>
       </c>
@@ -11717,8 +12877,8 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="10"/>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="11"/>
       <c r="B24" s="3" t="s">
         <v>47</v>
       </c>
@@ -11726,8 +12886,8 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="10"/>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="11"/>
       <c r="B25" s="3" t="s">
         <v>49</v>
       </c>
@@ -11735,8 +12895,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="10"/>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="11"/>
       <c r="B26" s="3" t="s">
         <v>51</v>
       </c>
@@ -11744,8 +12904,8 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="10"/>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="11"/>
       <c r="B27" s="3" t="s">
         <v>53</v>
       </c>
@@ -11753,8 +12913,8 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="10"/>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="11"/>
       <c r="B28" s="3" t="s">
         <v>55</v>
       </c>
@@ -11762,8 +12922,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="10"/>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="11"/>
       <c r="B29" s="3" t="s">
         <v>57</v>
       </c>
@@ -11771,8 +12931,8 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="10"/>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="11"/>
       <c r="B30" s="3" t="s">
         <v>59</v>
       </c>
@@ -11780,8 +12940,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="10"/>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="11"/>
       <c r="B31" s="3" t="s">
         <v>61</v>
       </c>
@@ -11789,8 +12949,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="10"/>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="11"/>
       <c r="B32" s="3" t="s">
         <v>63</v>
       </c>
@@ -11798,8 +12958,8 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="10"/>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="11"/>
       <c r="B33" s="3" t="s">
         <v>65</v>
       </c>
@@ -11807,8 +12967,8 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="10"/>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="11"/>
       <c r="B34" s="3" t="s">
         <v>67</v>
       </c>
@@ -11816,8 +12976,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="10"/>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="11"/>
       <c r="B35" s="3" t="s">
         <v>69</v>
       </c>
@@ -11825,8 +12985,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="11"/>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="12"/>
       <c r="B36" s="5" t="s">
         <v>71</v>
       </c>
@@ -11834,8 +12994,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="14" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="9" t="s">
         <v>45</v>
       </c>
       <c r="B37" s="3" t="s">
@@ -11845,8 +13005,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="14"/>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="9"/>
       <c r="B38" s="3" t="s">
         <v>75</v>
       </c>
@@ -11854,8 +13014,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="14"/>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" s="9"/>
       <c r="B39" s="3" t="s">
         <v>77</v>
       </c>
@@ -11863,8 +13023,8 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="9"/>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" s="10"/>
       <c r="B40" s="5" t="s">
         <v>79</v>
       </c>
@@ -11872,8 +13032,8 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="14" t="s">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" s="9" t="s">
         <v>47</v>
       </c>
       <c r="B41" s="3" t="s">
@@ -11883,8 +13043,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="14"/>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" s="9"/>
       <c r="B42" s="3" t="s">
         <v>83</v>
       </c>
@@ -11892,8 +13052,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="14"/>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" s="9"/>
       <c r="B43" s="3" t="s">
         <v>85</v>
       </c>
@@ -11901,8 +13061,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="14"/>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" s="9"/>
       <c r="B44" s="3" t="s">
         <v>87</v>
       </c>
@@ -11910,8 +13070,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="14"/>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" s="9"/>
       <c r="B45" s="3" t="s">
         <v>89</v>
       </c>
@@ -11919,8 +13079,8 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="14"/>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" s="9"/>
       <c r="B46" s="3" t="s">
         <v>91</v>
       </c>
@@ -11928,8 +13088,8 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="14"/>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" s="9"/>
       <c r="B47" s="3" t="s">
         <v>93</v>
       </c>
@@ -11937,8 +13097,8 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="14"/>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" s="9"/>
       <c r="B48" s="3" t="s">
         <v>95</v>
       </c>
@@ -11946,8 +13106,8 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="9"/>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" s="10"/>
       <c r="B49" s="5" t="s">
         <v>97</v>
       </c>
@@ -11955,8 +13115,8 @@
         <v>98</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="9" t="s">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" s="10" t="s">
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
@@ -11966,8 +13126,8 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="9" t="s">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" s="10" t="s">
         <v>51</v>
       </c>
       <c r="B51" s="5" t="s">
@@ -11977,8 +13137,8 @@
         <v>102</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="14" t="s">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" s="9" t="s">
         <v>53</v>
       </c>
       <c r="B52" s="3" t="s">
@@ -11988,8 +13148,8 @@
         <v>104</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="14"/>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" s="9"/>
       <c r="B53" s="3" t="s">
         <v>105</v>
       </c>
@@ -11997,8 +13157,8 @@
         <v>106</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="14"/>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" s="9"/>
       <c r="B54" s="3" t="s">
         <v>107</v>
       </c>
@@ -12006,8 +13166,8 @@
         <v>108</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="14"/>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" s="9"/>
       <c r="B55" s="3" t="s">
         <v>109</v>
       </c>
@@ -12015,8 +13175,8 @@
         <v>110</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="14"/>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56" s="9"/>
       <c r="B56" s="3" t="s">
         <v>111</v>
       </c>
@@ -12024,8 +13184,8 @@
         <v>112</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="14"/>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" s="9"/>
       <c r="B57" s="3" t="s">
         <v>113</v>
       </c>
@@ -12033,8 +13193,8 @@
         <v>114</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="14"/>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58" s="9"/>
       <c r="B58" s="3" t="s">
         <v>115</v>
       </c>
@@ -12042,8 +13202,8 @@
         <v>116</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="14"/>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59" s="9"/>
       <c r="B59" s="3" t="s">
         <v>117</v>
       </c>
@@ -12051,8 +13211,8 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="14"/>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60" s="9"/>
       <c r="B60" s="3" t="s">
         <v>119</v>
       </c>
@@ -12060,8 +13220,8 @@
         <v>120</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="14"/>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61" s="9"/>
       <c r="B61" s="3" t="s">
         <v>121</v>
       </c>
@@ -12069,8 +13229,8 @@
         <v>122</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="14"/>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62" s="9"/>
       <c r="B62" s="3" t="s">
         <v>123</v>
       </c>
@@ -12078,8 +13238,8 @@
         <v>124</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="14"/>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63" s="9"/>
       <c r="B63" s="3" t="s">
         <v>125</v>
       </c>
@@ -12087,8 +13247,8 @@
         <v>126</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="14"/>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A64" s="9"/>
       <c r="B64" s="3" t="s">
         <v>127</v>
       </c>
@@ -12096,8 +13256,8 @@
         <v>128</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="14"/>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65" s="9"/>
       <c r="B65" s="3" t="s">
         <v>129</v>
       </c>
@@ -12105,8 +13265,8 @@
         <v>130</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="14"/>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66" s="9"/>
       <c r="B66" s="3" t="s">
         <v>131</v>
       </c>
@@ -12114,8 +13274,8 @@
         <v>132</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="14"/>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67" s="9"/>
       <c r="B67" s="3" t="s">
         <v>133</v>
       </c>
@@ -12123,8 +13283,8 @@
         <v>134</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="14"/>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A68" s="9"/>
       <c r="B68" s="3" t="s">
         <v>135</v>
       </c>
@@ -12132,8 +13292,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="14"/>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A69" s="9"/>
       <c r="B69" s="3" t="s">
         <v>137</v>
       </c>
@@ -12141,8 +13301,8 @@
         <v>138</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="14"/>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A70" s="9"/>
       <c r="B70" s="3" t="s">
         <v>139</v>
       </c>
@@ -12150,8 +13310,8 @@
         <v>140</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="14"/>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A71" s="9"/>
       <c r="B71" s="3" t="s">
         <v>141</v>
       </c>
@@ -12159,8 +13319,8 @@
         <v>142</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="14"/>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A72" s="9"/>
       <c r="B72" s="3" t="s">
         <v>143</v>
       </c>
@@ -12168,8 +13328,8 @@
         <v>144</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="14"/>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A73" s="9"/>
       <c r="B73" s="3" t="s">
         <v>145</v>
       </c>
@@ -12177,8 +13337,8 @@
         <v>146</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="14"/>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A74" s="9"/>
       <c r="B74" s="3" t="s">
         <v>147</v>
       </c>
@@ -12186,8 +13346,8 @@
         <v>148</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="14"/>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A75" s="9"/>
       <c r="B75" s="3" t="s">
         <v>149</v>
       </c>
@@ -12195,8 +13355,8 @@
         <v>150</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="9"/>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A76" s="10"/>
       <c r="B76" s="5" t="s">
         <v>151</v>
       </c>
@@ -12204,8 +13364,8 @@
         <v>152</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="14" t="s">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A77" s="9" t="s">
         <v>55</v>
       </c>
       <c r="B77" s="3" t="s">
@@ -12215,8 +13375,8 @@
         <v>154</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="14"/>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A78" s="9"/>
       <c r="B78" s="3" t="s">
         <v>155</v>
       </c>
@@ -12224,8 +13384,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="14"/>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A79" s="9"/>
       <c r="B79" s="3" t="s">
         <v>157</v>
       </c>
@@ -12233,8 +13393,8 @@
         <v>158</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="14"/>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A80" s="9"/>
       <c r="B80" s="3" t="s">
         <v>159</v>
       </c>
@@ -12242,8 +13402,8 @@
         <v>160</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="14"/>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A81" s="9"/>
       <c r="B81" s="3" t="s">
         <v>161</v>
       </c>
@@ -12251,8 +13411,8 @@
         <v>162</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="14"/>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A82" s="9"/>
       <c r="B82" s="3" t="s">
         <v>163</v>
       </c>
@@ -12260,8 +13420,8 @@
         <v>164</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="9"/>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A83" s="10"/>
       <c r="B83" s="5" t="s">
         <v>165</v>
       </c>
@@ -12269,8 +13429,8 @@
         <v>166</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="14" t="s">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A84" s="9" t="s">
         <v>57</v>
       </c>
       <c r="B84" s="3" t="s">
@@ -12280,8 +13440,8 @@
         <v>168</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="14"/>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A85" s="9"/>
       <c r="B85" s="3" t="s">
         <v>169</v>
       </c>
@@ -12289,8 +13449,8 @@
         <v>170</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="14"/>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A86" s="9"/>
       <c r="B86" s="3" t="s">
         <v>171</v>
       </c>
@@ -12298,8 +13458,8 @@
         <v>172</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="9"/>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A87" s="10"/>
       <c r="B87" s="5" t="s">
         <v>173</v>
       </c>
@@ -12307,8 +13467,8 @@
         <v>174</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="14" t="s">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A88" s="9" t="s">
         <v>59</v>
       </c>
       <c r="B88" s="3" t="s">
@@ -12318,8 +13478,8 @@
         <v>176</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="14"/>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A89" s="9"/>
       <c r="B89" s="3" t="s">
         <v>177</v>
       </c>
@@ -12327,8 +13487,8 @@
         <v>178</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="14"/>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A90" s="9"/>
       <c r="B90" s="3" t="s">
         <v>179</v>
       </c>
@@ -12336,8 +13496,8 @@
         <v>180</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="14"/>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A91" s="9"/>
       <c r="B91" s="3" t="s">
         <v>181</v>
       </c>
@@ -12345,8 +13505,8 @@
         <v>182</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="9"/>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A92" s="10"/>
       <c r="B92" s="5" t="s">
         <v>183</v>
       </c>
@@ -12354,8 +13514,8 @@
         <v>184</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="9" t="s">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A93" s="10" t="s">
         <v>61</v>
       </c>
       <c r="B93" s="5" t="s">
@@ -12365,8 +13525,8 @@
         <v>186</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="14" t="s">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A94" s="9" t="s">
         <v>63</v>
       </c>
       <c r="B94" s="3" t="s">
@@ -12376,8 +13536,8 @@
         <v>188</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="14"/>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A95" s="9"/>
       <c r="B95" s="3" t="s">
         <v>189</v>
       </c>
@@ -12385,8 +13545,8 @@
         <v>190</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="9"/>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A96" s="10"/>
       <c r="B96" s="5" t="s">
         <v>191</v>
       </c>
@@ -12394,8 +13554,8 @@
         <v>192</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="14" t="s">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A97" s="9" t="s">
         <v>65</v>
       </c>
       <c r="B97" s="3" t="s">
@@ -12405,8 +13565,8 @@
         <v>194</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="14"/>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A98" s="9"/>
       <c r="B98" s="3" t="s">
         <v>195</v>
       </c>
@@ -12414,8 +13574,8 @@
         <v>196</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="14"/>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A99" s="9"/>
       <c r="B99" s="3" t="s">
         <v>197</v>
       </c>
@@ -12423,8 +13583,8 @@
         <v>198</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="14"/>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A100" s="9"/>
       <c r="B100" s="3" t="s">
         <v>199</v>
       </c>
@@ -12432,8 +13592,8 @@
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="9"/>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A101" s="10"/>
       <c r="B101" s="5" t="s">
         <v>201</v>
       </c>
@@ -12441,8 +13601,8 @@
         <v>202</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="14" t="s">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A102" s="9" t="s">
         <v>67</v>
       </c>
       <c r="B102" s="3" t="s">
@@ -12452,8 +13612,8 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="14"/>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A103" s="9"/>
       <c r="B103" s="3" t="s">
         <v>205</v>
       </c>
@@ -12461,8 +13621,8 @@
         <v>206</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="14"/>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A104" s="9"/>
       <c r="B104" s="3" t="s">
         <v>207</v>
       </c>
@@ -12470,8 +13630,8 @@
         <v>208</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="14"/>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A105" s="9"/>
       <c r="B105" s="3" t="s">
         <v>209</v>
       </c>
@@ -12479,8 +13639,8 @@
         <v>210</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="14"/>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A106" s="9"/>
       <c r="B106" s="3" t="s">
         <v>211</v>
       </c>
@@ -12488,8 +13648,8 @@
         <v>212</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="14"/>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A107" s="9"/>
       <c r="B107" s="3" t="s">
         <v>213</v>
       </c>
@@ -12497,8 +13657,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="9"/>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A108" s="10"/>
       <c r="B108" s="5" t="s">
         <v>215</v>
       </c>
@@ -12506,8 +13666,8 @@
         <v>216</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="14" t="s">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A109" s="9" t="s">
         <v>69</v>
       </c>
       <c r="B109" s="3" t="s">
@@ -12517,8 +13677,8 @@
         <v>218</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="14"/>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A110" s="9"/>
       <c r="B110" s="3" t="s">
         <v>219</v>
       </c>
@@ -12526,8 +13686,8 @@
         <v>220</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="14"/>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A111" s="9"/>
       <c r="B111" s="3" t="s">
         <v>221</v>
       </c>
@@ -12535,8 +13695,8 @@
         <v>222</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="9"/>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A112" s="10"/>
       <c r="B112" s="5" t="s">
         <v>223</v>
       </c>
@@ -12544,8 +13704,8 @@
         <v>224</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="9" t="s">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A113" s="10" t="s">
         <v>71</v>
       </c>
       <c r="B113" s="5" t="s">
@@ -12558,6 +13718,16 @@
   </sheetData>
   <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="19">
+    <mergeCell ref="A1"/>
+    <mergeCell ref="A2:A16"/>
+    <mergeCell ref="A17:C18"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A22:A36"/>
+    <mergeCell ref="A37:A40"/>
+    <mergeCell ref="A41:A49"/>
+    <mergeCell ref="A50"/>
+    <mergeCell ref="A51"/>
+    <mergeCell ref="A52:A76"/>
     <mergeCell ref="A97:A101"/>
     <mergeCell ref="A102:A108"/>
     <mergeCell ref="A109:A112"/>
@@ -12567,16 +13737,6 @@
     <mergeCell ref="A88:A92"/>
     <mergeCell ref="A93"/>
     <mergeCell ref="A94:A96"/>
-    <mergeCell ref="A37:A40"/>
-    <mergeCell ref="A41:A49"/>
-    <mergeCell ref="A50"/>
-    <mergeCell ref="A51"/>
-    <mergeCell ref="A52:A76"/>
-    <mergeCell ref="A1"/>
-    <mergeCell ref="A2:A16"/>
-    <mergeCell ref="A17:C18"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A22:A36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12585,7 +13745,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BH15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -12607,7 +13767,7 @@
     <col min="22" max="60" width="12" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -12789,7 +13949,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="2" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -12968,7 +14128,7 @@
         <v>2.6667000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -13147,7 +14307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -13326,7 +14486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -13505,7 +14665,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="6" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -13684,7 +14844,7 @@
         <v>0.5333</v>
       </c>
     </row>
-    <row r="7" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -13863,7 +15023,7 @@
         <v>10.666700000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -14042,7 +15202,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="9" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -14221,7 +15381,7 @@
         <v>0.5333</v>
       </c>
     </row>
-    <row r="10" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -14400,7 +15560,7 @@
         <v>2.6667000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -14579,7 +15739,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="12" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -14758,7 +15918,7 @@
         <v>8.8888999999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -14937,7 +16097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -15116,7 +16276,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -15304,7 +16464,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:V15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -15315,7 +16475,7 @@
     <col min="11" max="22" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -15383,7 +16543,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -15451,7 +16611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -15519,7 +16679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -15587,7 +16747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -15655,7 +16815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -15723,7 +16883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -15791,7 +16951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -15859,7 +17019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -15927,7 +17087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -15995,7 +17155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -16063,7 +17223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -16131,7 +17291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -16199,7 +17359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -16267,7 +17427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -16344,7 +17504,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AK15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -16355,7 +17515,7 @@
     <col min="11" max="37" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -16468,7 +17628,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -16581,7 +17741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -16694,7 +17854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -16807,7 +17967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -16920,7 +18080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -17033,7 +18193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -17146,7 +18306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -17259,7 +18419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -17372,7 +18532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -17485,7 +18645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -17598,7 +18758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -17711,7 +18871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -17824,7 +18984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -17937,7 +19097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -18059,7 +19219,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -18069,7 +19229,7 @@
     <col min="8" max="10" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -18101,7 +19261,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -18133,7 +19293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -18165,7 +19325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -18197,7 +19357,7 @@
         <v>0.94120000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -18229,7 +19389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -18261,7 +19421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -18293,7 +19453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -18325,7 +19485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -18357,7 +19517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -18389,7 +19549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -18421,7 +19581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -18453,7 +19613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -18485,7 +19645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -18517,7 +19677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -18558,7 +19718,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -18568,7 +19728,7 @@
     <col min="8" max="10" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -18600,7 +19760,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -18632,7 +19792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -18664,7 +19824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -18696,7 +19856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -18728,7 +19888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -18760,7 +19920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -18792,7 +19952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -18824,7 +19984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -18856,7 +20016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -18888,7 +20048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -18920,7 +20080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -18952,7 +20112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -18984,7 +20144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -19016,7 +20176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -19057,7 +20217,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:CG15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -19068,7 +20228,7 @@
     <col min="11" max="85" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -19325,7 +20485,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="2" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -19582,7 +20742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -19839,7 +20999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -20096,7 +21256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -20353,7 +21513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -20610,7 +21770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -20867,7 +22027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -21124,7 +22284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -21381,7 +22541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -21638,7 +22798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -21895,7 +23055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -22152,7 +23312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -22409,7 +23569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -22666,7 +23826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -22932,7 +24092,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:AE15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -22943,7 +24103,7 @@
     <col min="11" max="31" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -23038,7 +24198,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -23133,7 +24293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -23228,7 +24388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -23323,7 +24483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -23418,7 +24578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -23513,7 +24673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -23608,7 +24768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -23703,7 +24863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -23798,7 +24958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -23893,7 +25053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -23988,7 +25148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -24083,7 +25243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -24178,7 +25338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -24273,7 +25433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
